--- a/research/traditional_assets/database/data/cyprus/cyprus_precious_metals.xlsx
+++ b/research/traditional_assets/database/data/cyprus/cyprus_precious_metals.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1071955603824255</v>
+        <v>0.1071009409319474</v>
       </c>
       <c r="C2">
-        <v>363.422189576648</v>
+        <v>360.0491152187439</v>
       </c>
       <c r="D2">
-        <v>145.722189576648</v>
+        <v>145.9471152187439</v>
       </c>
       <c r="E2">
-        <v>-106.2</v>
+        <v>-102.602</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>3.598</v>
       </c>
       <c r="G2">
         <v>217.7</v>
@@ -1451,28 +1451,28 @@
         <v>170.41</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.1809794</v>
       </c>
       <c r="N2">
-        <v>170.41</v>
+        <v>170.2290206</v>
       </c>
       <c r="O2">
-        <v>21.30125</v>
+        <v>21.278627575</v>
       </c>
       <c r="P2">
-        <v>149.10875</v>
+        <v>148.950393025</v>
       </c>
       <c r="Q2">
-        <v>152.49875</v>
+        <v>152.340393025</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1071955603824255</v>
+        <v>0.107738197911058</v>
       </c>
       <c r="T2">
-        <v>1.035217350236429</v>
+        <v>1.044366998533973</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>941.5988781043588</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1071009409319474</v>
+        <v>0.1070063214814694</v>
       </c>
       <c r="C3">
-        <v>360.0491152187439</v>
+        <v>356.6767362903358</v>
       </c>
       <c r="D3">
-        <v>145.9471152187439</v>
+        <v>146.1727362903358</v>
       </c>
       <c r="E3">
-        <v>-102.602</v>
+        <v>-99.004</v>
       </c>
       <c r="F3">
-        <v>3.598</v>
+        <v>7.196000000000001</v>
       </c>
       <c r="G3">
         <v>217.7</v>
@@ -1533,28 +1533,28 @@
         <v>170.41</v>
       </c>
       <c r="M3">
-        <v>0.1809794</v>
+        <v>0.3619588</v>
       </c>
       <c r="N3">
-        <v>170.2290206</v>
+        <v>170.0480412</v>
       </c>
       <c r="O3">
-        <v>21.278627575</v>
+        <v>21.25600515</v>
       </c>
       <c r="P3">
-        <v>148.950393025</v>
+        <v>148.79203605</v>
       </c>
       <c r="Q3">
-        <v>152.340393025</v>
+        <v>152.18203605</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.107738197911058</v>
+        <v>0.1082919096749688</v>
       </c>
       <c r="T3">
-        <v>1.044366998533973</v>
+        <v>1.053703374347794</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>941.5988781043588</v>
+        <v>470.7994390521795</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1070063214814694</v>
+        <v>0.1069117020309914</v>
       </c>
       <c r="C4">
-        <v>356.6767362903358</v>
+        <v>353.3050560216313</v>
       </c>
       <c r="D4">
-        <v>146.1727362903358</v>
+        <v>146.3990560216313</v>
       </c>
       <c r="E4">
-        <v>-99.004</v>
+        <v>-95.40600000000001</v>
       </c>
       <c r="F4">
-        <v>7.196000000000001</v>
+        <v>10.794</v>
       </c>
       <c r="G4">
         <v>217.7</v>
@@ -1615,28 +1615,28 @@
         <v>170.41</v>
       </c>
       <c r="M4">
-        <v>0.3619588</v>
+        <v>0.5429382</v>
       </c>
       <c r="N4">
-        <v>170.0480412</v>
+        <v>169.8670618</v>
       </c>
       <c r="O4">
-        <v>21.25600515</v>
+        <v>21.233382725</v>
       </c>
       <c r="P4">
-        <v>148.79203605</v>
+        <v>148.633679075</v>
       </c>
       <c r="Q4">
-        <v>152.18203605</v>
+        <v>152.023679075</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1082919096749688</v>
+        <v>0.1088570381762798</v>
       </c>
       <c r="T4">
-        <v>1.053703374347794</v>
+        <v>1.063232252755714</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>470.7994390521795</v>
+        <v>313.8662927014529</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1069117020309914</v>
+        <v>0.1068170825805133</v>
       </c>
       <c r="C5">
-        <v>353.3050560216313</v>
+        <v>349.934077662874</v>
       </c>
       <c r="D5">
-        <v>146.3990560216313</v>
+        <v>146.626077662874</v>
       </c>
       <c r="E5">
-        <v>-95.40600000000001</v>
+        <v>-91.80800000000001</v>
       </c>
       <c r="F5">
-        <v>10.794</v>
+        <v>14.392</v>
       </c>
       <c r="G5">
         <v>217.7</v>
@@ -1697,28 +1697,28 @@
         <v>170.41</v>
       </c>
       <c r="M5">
-        <v>0.5429382</v>
+        <v>0.7239176</v>
       </c>
       <c r="N5">
-        <v>169.8670618</v>
+        <v>169.6860824</v>
       </c>
       <c r="O5">
-        <v>21.233382725</v>
+        <v>21.2107603</v>
       </c>
       <c r="P5">
-        <v>148.633679075</v>
+        <v>148.4753221</v>
       </c>
       <c r="Q5">
-        <v>152.023679075</v>
+        <v>151.8653221</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1088570381762798</v>
+        <v>0.1094339401880347</v>
       </c>
       <c r="T5">
-        <v>1.063232252755714</v>
+        <v>1.072959649463799</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>313.8662927014529</v>
+        <v>235.3997195260897</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1068170825805133</v>
+        <v>0.1067224631300353</v>
       </c>
       <c r="C6">
-        <v>349.934077662874</v>
+        <v>346.5638044844997</v>
       </c>
       <c r="D6">
-        <v>146.626077662874</v>
+        <v>146.8538044844997</v>
       </c>
       <c r="E6">
-        <v>-91.80800000000001</v>
+        <v>-88.21000000000001</v>
       </c>
       <c r="F6">
-        <v>14.392</v>
+        <v>17.99</v>
       </c>
       <c r="G6">
         <v>217.7</v>
@@ -1779,28 +1779,28 @@
         <v>170.41</v>
       </c>
       <c r="M6">
-        <v>0.7239176</v>
+        <v>0.9048970000000001</v>
       </c>
       <c r="N6">
-        <v>169.6860824</v>
+        <v>169.505103</v>
       </c>
       <c r="O6">
-        <v>21.2107603</v>
+        <v>21.188137875</v>
       </c>
       <c r="P6">
-        <v>148.4753221</v>
+        <v>148.316965125</v>
       </c>
       <c r="Q6">
-        <v>151.8653221</v>
+        <v>151.706965125</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1094339401880347</v>
+        <v>0.1100229875053003</v>
       </c>
       <c r="T6">
-        <v>1.072959649463799</v>
+        <v>1.082891833471001</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>235.3997195260897</v>
+        <v>188.3197756208718</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1067224631300353</v>
+        <v>0.1066278436795573</v>
       </c>
       <c r="C7">
-        <v>346.5638044844997</v>
+        <v>343.1942397772931</v>
       </c>
       <c r="D7">
-        <v>146.8538044844997</v>
+        <v>147.0822397772931</v>
       </c>
       <c r="E7">
-        <v>-88.21000000000001</v>
+        <v>-84.61199999999999</v>
       </c>
       <c r="F7">
-        <v>17.99</v>
+        <v>21.588</v>
       </c>
       <c r="G7">
         <v>217.7</v>
@@ -1861,28 +1861,28 @@
         <v>170.41</v>
       </c>
       <c r="M7">
-        <v>0.9048970000000001</v>
+        <v>1.0858764</v>
       </c>
       <c r="N7">
-        <v>169.505103</v>
+        <v>169.3241236</v>
       </c>
       <c r="O7">
-        <v>21.188137875</v>
+        <v>21.16551545</v>
       </c>
       <c r="P7">
-        <v>148.316965125</v>
+        <v>148.15860815</v>
       </c>
       <c r="Q7">
-        <v>151.706965125</v>
+        <v>151.54860815</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1100229875053003</v>
+        <v>0.1106245677442099</v>
       </c>
       <c r="T7">
-        <v>1.082891833471001</v>
+        <v>1.093035340542187</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>188.3197756208718</v>
+        <v>156.9331463507265</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1066278436795573</v>
+        <v>0.1065332242290793</v>
       </c>
       <c r="C8">
-        <v>343.1942397772931</v>
+        <v>339.8253868525465</v>
       </c>
       <c r="D8">
-        <v>147.0822397772931</v>
+        <v>147.3113868525465</v>
       </c>
       <c r="E8">
-        <v>-84.61199999999999</v>
+        <v>-81.01400000000001</v>
       </c>
       <c r="F8">
-        <v>21.588</v>
+        <v>25.186</v>
       </c>
       <c r="G8">
         <v>217.7</v>
@@ -1943,28 +1943,28 @@
         <v>170.41</v>
       </c>
       <c r="M8">
-        <v>1.0858764</v>
+        <v>1.2668558</v>
       </c>
       <c r="N8">
-        <v>169.3241236</v>
+        <v>169.1431442</v>
       </c>
       <c r="O8">
-        <v>21.16551545</v>
+        <v>21.142893025</v>
       </c>
       <c r="P8">
-        <v>148.15860815</v>
+        <v>148.000251175</v>
       </c>
       <c r="Q8">
-        <v>151.54860815</v>
+        <v>151.390251175</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1106245677442099</v>
+        <v>0.1112390851925583</v>
       </c>
       <c r="T8">
-        <v>1.093035340542187</v>
+        <v>1.103396987550388</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>156.9331463507265</v>
+        <v>134.5141254434799</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1065332242290793</v>
+        <v>0.1064386047786012</v>
       </c>
       <c r="C9">
-        <v>339.8253868525466</v>
+        <v>336.4572490422198</v>
       </c>
       <c r="D9">
-        <v>147.3113868525465</v>
+        <v>147.5412490422198</v>
       </c>
       <c r="E9">
-        <v>-81.014</v>
+        <v>-77.416</v>
       </c>
       <c r="F9">
-        <v>25.186</v>
+        <v>28.784</v>
       </c>
       <c r="G9">
         <v>217.7</v>
@@ -2025,28 +2025,28 @@
         <v>170.41</v>
       </c>
       <c r="M9">
-        <v>1.2668558</v>
+        <v>1.4478352</v>
       </c>
       <c r="N9">
-        <v>169.1431442</v>
+        <v>168.9621648</v>
       </c>
       <c r="O9">
-        <v>21.142893025</v>
+        <v>21.1202706</v>
       </c>
       <c r="P9">
-        <v>148.000251175</v>
+        <v>147.8418942</v>
       </c>
       <c r="Q9">
-        <v>151.390251175</v>
+        <v>151.2318942</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1112390851925583</v>
+        <v>0.1118669617158709</v>
       </c>
       <c r="T9">
-        <v>1.103396987550388</v>
+        <v>1.113983887754418</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>134.5141254434799</v>
+        <v>117.6998597630449</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1064386047786012</v>
+        <v>0.1063439853281232</v>
       </c>
       <c r="C10">
-        <v>336.4572490422198</v>
+        <v>333.0898296991019</v>
       </c>
       <c r="D10">
-        <v>147.5412490422198</v>
+        <v>147.7718296991019</v>
       </c>
       <c r="E10">
-        <v>-77.416</v>
+        <v>-73.81800000000001</v>
       </c>
       <c r="F10">
-        <v>28.784</v>
+        <v>32.382</v>
       </c>
       <c r="G10">
         <v>217.7</v>
@@ -2107,28 +2107,28 @@
         <v>170.41</v>
       </c>
       <c r="M10">
-        <v>1.4478352</v>
+        <v>1.6288146</v>
       </c>
       <c r="N10">
-        <v>168.9621648</v>
+        <v>168.7811854</v>
       </c>
       <c r="O10">
-        <v>21.1202706</v>
+        <v>21.097648175</v>
       </c>
       <c r="P10">
-        <v>147.8418942</v>
+        <v>147.683537225</v>
       </c>
       <c r="Q10">
-        <v>151.2318942</v>
+        <v>151.073537225</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1118669617158709</v>
+        <v>0.1125086377232123</v>
       </c>
       <c r="T10">
-        <v>1.113983887754418</v>
+        <v>1.124803467083812</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>117.6998597630449</v>
+        <v>104.622097567151</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1063439853281232</v>
+        <v>0.1062493658776452</v>
       </c>
       <c r="C11">
-        <v>333.0898296991019</v>
+        <v>329.7231321969737</v>
       </c>
       <c r="D11">
-        <v>147.7718296991019</v>
+        <v>148.0031321969737</v>
       </c>
       <c r="E11">
-        <v>-73.81800000000001</v>
+        <v>-70.22</v>
       </c>
       <c r="F11">
-        <v>32.382</v>
+        <v>35.98</v>
       </c>
       <c r="G11">
         <v>217.7</v>
@@ -2189,28 +2189,28 @@
         <v>170.41</v>
       </c>
       <c r="M11">
-        <v>1.6288146</v>
+        <v>1.809794</v>
       </c>
       <c r="N11">
-        <v>168.7811854</v>
+        <v>168.600206</v>
       </c>
       <c r="O11">
-        <v>21.097648175</v>
+        <v>21.07502575</v>
       </c>
       <c r="P11">
-        <v>147.683537225</v>
+        <v>147.52518025</v>
       </c>
       <c r="Q11">
-        <v>151.073537225</v>
+        <v>150.91518025</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1125086377232123</v>
+        <v>0.1131645731973835</v>
       </c>
       <c r="T11">
-        <v>1.124803467083812</v>
+        <v>1.135863481509415</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>104.622097567151</v>
+        <v>94.1598878104359</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1062493658776452</v>
+        <v>0.1061547464271671</v>
       </c>
       <c r="C12">
-        <v>329.7231321969737</v>
+        <v>326.3571599307727</v>
       </c>
       <c r="D12">
-        <v>148.0031321969737</v>
+        <v>148.2351599307727</v>
       </c>
       <c r="E12">
-        <v>-70.22</v>
+        <v>-66.622</v>
       </c>
       <c r="F12">
-        <v>35.98</v>
+        <v>39.578</v>
       </c>
       <c r="G12">
         <v>217.7</v>
@@ -2271,28 +2271,28 @@
         <v>170.41</v>
       </c>
       <c r="M12">
-        <v>1.809794</v>
+        <v>1.9907734</v>
       </c>
       <c r="N12">
-        <v>168.600206</v>
+        <v>168.4192266</v>
       </c>
       <c r="O12">
-        <v>21.07502575</v>
+        <v>21.052403325</v>
       </c>
       <c r="P12">
-        <v>147.52518025</v>
+        <v>147.366823275</v>
       </c>
       <c r="Q12">
-        <v>150.91518025</v>
+        <v>150.756823275</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1131645731973835</v>
+        <v>0.1138352487945698</v>
       </c>
       <c r="T12">
-        <v>1.135863481509415</v>
+        <v>1.147172035585032</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>94.15988781043589</v>
+        <v>85.59989800948718</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1061547464271671</v>
+        <v>0.1060601269766891</v>
       </c>
       <c r="C13">
-        <v>326.3571599307727</v>
+        <v>322.9919163167589</v>
       </c>
       <c r="D13">
-        <v>148.2351599307727</v>
+        <v>148.467916316759</v>
       </c>
       <c r="E13">
-        <v>-66.622</v>
+        <v>-63.024</v>
       </c>
       <c r="F13">
-        <v>39.578</v>
+        <v>43.176</v>
       </c>
       <c r="G13">
         <v>217.7</v>
@@ -2353,28 +2353,28 @@
         <v>170.41</v>
       </c>
       <c r="M13">
-        <v>1.9907734</v>
+        <v>2.1717528</v>
       </c>
       <c r="N13">
-        <v>168.4192266</v>
+        <v>168.2382472</v>
       </c>
       <c r="O13">
-        <v>21.052403325</v>
+        <v>21.0297809</v>
       </c>
       <c r="P13">
-        <v>147.366823275</v>
+        <v>147.2084663</v>
       </c>
       <c r="Q13">
-        <v>150.756823275</v>
+        <v>150.5984663</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1138352487945698</v>
+        <v>0.1145211670189649</v>
       </c>
       <c r="T13">
-        <v>1.147172035585032</v>
+        <v>1.158737602253276</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>85.59989800948718</v>
+        <v>78.46657317536324</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1060601269766891</v>
+        <v>0.1059655075262111</v>
       </c>
       <c r="C14">
-        <v>322.9919163167589</v>
+        <v>319.6274047926833</v>
       </c>
       <c r="D14">
-        <v>148.467916316759</v>
+        <v>148.7014047926833</v>
       </c>
       <c r="E14">
-        <v>-63.024</v>
+        <v>-59.426</v>
       </c>
       <c r="F14">
-        <v>43.176</v>
+        <v>46.774</v>
       </c>
       <c r="G14">
         <v>217.7</v>
@@ -2435,28 +2435,28 @@
         <v>170.41</v>
       </c>
       <c r="M14">
-        <v>2.1717528</v>
+        <v>2.3527322</v>
       </c>
       <c r="N14">
-        <v>168.2382472</v>
+        <v>168.0572678</v>
       </c>
       <c r="O14">
-        <v>21.0297809</v>
+        <v>21.007158475</v>
       </c>
       <c r="P14">
-        <v>147.2084663</v>
+        <v>147.050109325</v>
       </c>
       <c r="Q14">
-        <v>150.5984663</v>
+        <v>150.440109325</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1145211670189649</v>
+        <v>0.1152228534784035</v>
       </c>
       <c r="T14">
-        <v>1.158737602253276</v>
+        <v>1.170569044017342</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>78.46657317536324</v>
+        <v>72.43068293110454</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1059655075262111</v>
+        <v>0.105870888075733</v>
       </c>
       <c r="C15">
-        <v>319.6274047926833</v>
+        <v>316.2636288179559</v>
       </c>
       <c r="D15">
-        <v>148.7014047926833</v>
+        <v>148.9356288179559</v>
       </c>
       <c r="E15">
-        <v>-59.426</v>
+        <v>-55.828</v>
       </c>
       <c r="F15">
-        <v>46.774</v>
+        <v>50.37200000000001</v>
       </c>
       <c r="G15">
         <v>217.7</v>
@@ -2517,28 +2517,28 @@
         <v>170.41</v>
       </c>
       <c r="M15">
-        <v>2.3527322</v>
+        <v>2.5337116</v>
       </c>
       <c r="N15">
-        <v>168.0572678</v>
+        <v>167.8762884</v>
       </c>
       <c r="O15">
-        <v>21.007158475</v>
+        <v>20.98453605</v>
       </c>
       <c r="P15">
-        <v>147.050109325</v>
+        <v>146.89175235</v>
       </c>
       <c r="Q15">
-        <v>150.440109325</v>
+        <v>150.28175235</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1152228534784035</v>
+        <v>0.1159408582275966</v>
       </c>
       <c r="T15">
-        <v>1.170569044017342</v>
+        <v>1.182675635589874</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>72.43068293110454</v>
+        <v>67.25706272173993</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.105870888075733</v>
+        <v>0.105776268625255</v>
       </c>
       <c r="C16">
-        <v>316.2636288179559</v>
+        <v>312.9005918738172</v>
       </c>
       <c r="D16">
-        <v>148.9356288179559</v>
+        <v>149.1705918738173</v>
       </c>
       <c r="E16">
-        <v>-55.828</v>
+        <v>-52.22999999999999</v>
       </c>
       <c r="F16">
-        <v>50.37200000000001</v>
+        <v>53.97000000000001</v>
       </c>
       <c r="G16">
         <v>217.7</v>
@@ -2599,28 +2599,28 @@
         <v>170.41</v>
       </c>
       <c r="M16">
-        <v>2.5337116</v>
+        <v>2.714691000000001</v>
       </c>
       <c r="N16">
-        <v>167.8762884</v>
+        <v>167.695309</v>
       </c>
       <c r="O16">
-        <v>20.98453605</v>
+        <v>20.961913625</v>
       </c>
       <c r="P16">
-        <v>146.89175235</v>
+        <v>146.733395375</v>
       </c>
       <c r="Q16">
-        <v>150.28175235</v>
+        <v>150.123395375</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1159408582275966</v>
+        <v>0.1166757572061823</v>
       </c>
       <c r="T16">
-        <v>1.182675635589874</v>
+        <v>1.195067088140584</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>67.25706272173993</v>
+        <v>62.77325854029059</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.105776268625255</v>
+        <v>0.105681649174777</v>
       </c>
       <c r="C17">
-        <v>312.9005918738173</v>
+        <v>309.5382974635112</v>
       </c>
       <c r="D17">
-        <v>149.1705918738173</v>
+        <v>149.4062974635112</v>
       </c>
       <c r="E17">
-        <v>-52.23</v>
+        <v>-48.632</v>
       </c>
       <c r="F17">
-        <v>53.97</v>
+        <v>57.568</v>
       </c>
       <c r="G17">
         <v>217.7</v>
@@ -2681,28 +2681,28 @@
         <v>170.41</v>
       </c>
       <c r="M17">
-        <v>2.714691</v>
+        <v>2.8956704</v>
       </c>
       <c r="N17">
-        <v>167.695309</v>
+        <v>167.5143296</v>
       </c>
       <c r="O17">
-        <v>20.961913625</v>
+        <v>20.9392912</v>
       </c>
       <c r="P17">
-        <v>146.733395375</v>
+        <v>146.5750384</v>
       </c>
       <c r="Q17">
-        <v>150.123395375</v>
+        <v>149.9650384</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1166757572061823</v>
+        <v>0.1174281537794964</v>
       </c>
       <c r="T17">
-        <v>1.195067088140583</v>
+        <v>1.207753575275834</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>62.77325854029061</v>
+        <v>58.84992988152243</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.105681649174777</v>
+        <v>0.105587029724299</v>
       </c>
       <c r="C18">
-        <v>309.5382974635112</v>
+        <v>306.1767491124581</v>
       </c>
       <c r="D18">
-        <v>149.4062974635112</v>
+        <v>149.6427491124581</v>
       </c>
       <c r="E18">
-        <v>-48.632</v>
+        <v>-45.034</v>
       </c>
       <c r="F18">
-        <v>57.568</v>
+        <v>61.166</v>
       </c>
       <c r="G18">
         <v>217.7</v>
@@ -2763,28 +2763,28 @@
         <v>170.41</v>
       </c>
       <c r="M18">
-        <v>2.8956704</v>
+        <v>3.0766498</v>
       </c>
       <c r="N18">
-        <v>167.5143296</v>
+        <v>167.3333502</v>
       </c>
       <c r="O18">
-        <v>20.9392912</v>
+        <v>20.916668775</v>
       </c>
       <c r="P18">
-        <v>146.5750384</v>
+        <v>146.416681425</v>
       </c>
       <c r="Q18">
-        <v>149.9650384</v>
+        <v>149.806681425</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1174281537794964</v>
+        <v>0.1181986803907216</v>
       </c>
       <c r="T18">
-        <v>1.207753575275834</v>
+        <v>1.220745760896271</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>58.84992988152243</v>
+        <v>55.3881693002564</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.105587029724299</v>
+        <v>0.1054924102738209</v>
       </c>
       <c r="C19">
-        <v>306.1767491124581</v>
+        <v>302.8159503684318</v>
       </c>
       <c r="D19">
-        <v>149.6427491124581</v>
+        <v>149.8799503684318</v>
       </c>
       <c r="E19">
-        <v>-45.034</v>
+        <v>-41.43599999999999</v>
       </c>
       <c r="F19">
-        <v>61.166</v>
+        <v>64.76400000000001</v>
       </c>
       <c r="G19">
         <v>217.7</v>
@@ -2845,28 +2845,28 @@
         <v>170.41</v>
       </c>
       <c r="M19">
-        <v>3.0766498</v>
+        <v>3.2576292</v>
       </c>
       <c r="N19">
-        <v>167.3333502</v>
+        <v>167.1523708</v>
       </c>
       <c r="O19">
-        <v>20.916668775</v>
+        <v>20.89404635</v>
       </c>
       <c r="P19">
-        <v>146.416681425</v>
+        <v>146.25832445</v>
       </c>
       <c r="Q19">
-        <v>149.806681425</v>
+        <v>149.64832445</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1181986803907216</v>
+        <v>0.1189880003339279</v>
       </c>
       <c r="T19">
-        <v>1.220745760896271</v>
+        <v>1.234054829092816</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>55.3881693002564</v>
+        <v>52.31104878357549</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1054924102738209</v>
+        <v>0.1053977908233429</v>
       </c>
       <c r="C20">
-        <v>302.8159503684318</v>
+        <v>299.4559048017357</v>
       </c>
       <c r="D20">
-        <v>149.8799503684318</v>
+        <v>150.1179048017358</v>
       </c>
       <c r="E20">
-        <v>-41.43600000000001</v>
+        <v>-37.83799999999999</v>
       </c>
       <c r="F20">
-        <v>64.764</v>
+        <v>68.36200000000001</v>
       </c>
       <c r="G20">
         <v>217.7</v>
@@ -2927,28 +2927,28 @@
         <v>170.41</v>
       </c>
       <c r="M20">
-        <v>3.2576292</v>
+        <v>3.4386086</v>
       </c>
       <c r="N20">
-        <v>167.1523708</v>
+        <v>166.9713914</v>
       </c>
       <c r="O20">
-        <v>20.89404635</v>
+        <v>20.871423925</v>
       </c>
       <c r="P20">
-        <v>146.25832445</v>
+        <v>146.099967475</v>
       </c>
       <c r="Q20">
-        <v>149.64832445</v>
+        <v>149.489967475</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1189880003339279</v>
+        <v>0.119796809658448</v>
       </c>
       <c r="T20">
-        <v>1.234054829092816</v>
+        <v>1.247692516257177</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>52.3110487835755</v>
+        <v>49.5578356897031</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1053977908233429</v>
+        <v>0.1053031713728649</v>
       </c>
       <c r="C21">
-        <v>299.4559048017357</v>
+        <v>296.0966160053831</v>
       </c>
       <c r="D21">
-        <v>150.1179048017358</v>
+        <v>150.3566160053831</v>
       </c>
       <c r="E21">
-        <v>-37.83799999999999</v>
+        <v>-34.23999999999999</v>
       </c>
       <c r="F21">
-        <v>68.36200000000001</v>
+        <v>71.96000000000001</v>
       </c>
       <c r="G21">
         <v>217.7</v>
@@ -3009,28 +3009,28 @@
         <v>170.41</v>
       </c>
       <c r="M21">
-        <v>3.4386086</v>
+        <v>3.619588</v>
       </c>
       <c r="N21">
-        <v>166.9713914</v>
+        <v>166.790412</v>
       </c>
       <c r="O21">
-        <v>20.871423925</v>
+        <v>20.8488015</v>
       </c>
       <c r="P21">
-        <v>146.099967475</v>
+        <v>145.9416105</v>
       </c>
       <c r="Q21">
-        <v>149.489967475</v>
+        <v>149.3316105</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.119796809658448</v>
+        <v>0.1206258392160811</v>
       </c>
       <c r="T21">
-        <v>1.247692516257177</v>
+        <v>1.261671145600648</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>49.5578356897031</v>
+        <v>47.07994390521795</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1053031713728649</v>
+        <v>0.1052085519223868</v>
       </c>
       <c r="C22">
-        <v>296.0966160053831</v>
+        <v>292.7380875952773</v>
       </c>
       <c r="D22">
-        <v>150.3566160053831</v>
+        <v>150.5960875952773</v>
       </c>
       <c r="E22">
-        <v>-34.23999999999999</v>
+        <v>-30.642</v>
       </c>
       <c r="F22">
-        <v>71.96000000000001</v>
+        <v>75.55800000000001</v>
       </c>
       <c r="G22">
         <v>217.7</v>
@@ -3091,28 +3091,28 @@
         <v>170.41</v>
       </c>
       <c r="M22">
-        <v>3.619588</v>
+        <v>3.8005674</v>
       </c>
       <c r="N22">
-        <v>166.790412</v>
+        <v>166.6094326</v>
       </c>
       <c r="O22">
-        <v>20.8488015</v>
+        <v>20.826179075</v>
       </c>
       <c r="P22">
-        <v>145.9416105</v>
+        <v>145.783253525</v>
       </c>
       <c r="Q22">
-        <v>149.3316105</v>
+        <v>149.173253525</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1206258392160811</v>
+        <v>0.1214758568637808</v>
       </c>
       <c r="T22">
-        <v>1.261671145600648</v>
+        <v>1.276003664294586</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>47.07994390521795</v>
+        <v>44.83804181449328</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1052085519223868</v>
+        <v>0.1051139324719088</v>
       </c>
       <c r="C23">
-        <v>292.7380875952773</v>
+        <v>289.3803232103945</v>
       </c>
       <c r="D23">
-        <v>150.5960875952773</v>
+        <v>150.8363232103945</v>
       </c>
       <c r="E23">
-        <v>-30.64200000000001</v>
+        <v>-27.044</v>
       </c>
       <c r="F23">
-        <v>75.55799999999999</v>
+        <v>79.15600000000001</v>
       </c>
       <c r="G23">
         <v>217.7</v>
@@ -3173,28 +3173,28 @@
         <v>170.41</v>
       </c>
       <c r="M23">
-        <v>3.800567399999999</v>
+        <v>3.9815468</v>
       </c>
       <c r="N23">
-        <v>166.6094326</v>
+        <v>166.4284532</v>
       </c>
       <c r="O23">
-        <v>20.826179075</v>
+        <v>20.80355665</v>
       </c>
       <c r="P23">
-        <v>145.783253525</v>
+        <v>145.62489655</v>
       </c>
       <c r="Q23">
-        <v>149.173253525</v>
+        <v>149.01489655</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1214758568637808</v>
+        <v>0.1223476698357805</v>
       </c>
       <c r="T23">
-        <v>1.276003664294586</v>
+        <v>1.290703683467855</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>44.83804181449329</v>
+        <v>42.79994900474359</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1051139324719088</v>
+        <v>0.1050193130214307</v>
       </c>
       <c r="C24">
-        <v>289.3803232103945</v>
+        <v>286.0233265129679</v>
       </c>
       <c r="D24">
-        <v>150.8363232103945</v>
+        <v>151.0773265129679</v>
       </c>
       <c r="E24">
-        <v>-27.044</v>
+        <v>-23.446</v>
       </c>
       <c r="F24">
-        <v>79.15600000000001</v>
+        <v>82.754</v>
       </c>
       <c r="G24">
         <v>217.7</v>
@@ -3255,28 +3255,28 @@
         <v>170.41</v>
       </c>
       <c r="M24">
-        <v>3.9815468</v>
+        <v>4.1625262</v>
       </c>
       <c r="N24">
-        <v>166.4284532</v>
+        <v>166.2474738</v>
       </c>
       <c r="O24">
-        <v>20.80355665</v>
+        <v>20.780934225</v>
       </c>
       <c r="P24">
-        <v>145.62489655</v>
+        <v>145.466539575</v>
       </c>
       <c r="Q24">
-        <v>149.01489655</v>
+        <v>148.856539575</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1223476698357805</v>
+        <v>0.1232421273005594</v>
       </c>
       <c r="T24">
-        <v>1.290703683467855</v>
+        <v>1.30578552132095</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>42.79994900474359</v>
+        <v>40.93908165671126</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1050193130214307</v>
+        <v>0.1049246935709527</v>
       </c>
       <c r="C25">
-        <v>286.0233265129679</v>
+        <v>282.6671011886741</v>
       </c>
       <c r="D25">
-        <v>151.0773265129679</v>
+        <v>151.3191011886742</v>
       </c>
       <c r="E25">
-        <v>-23.446</v>
+        <v>-19.848</v>
       </c>
       <c r="F25">
-        <v>82.754</v>
+        <v>86.352</v>
       </c>
       <c r="G25">
         <v>217.7</v>
@@ -3337,28 +3337,28 @@
         <v>170.41</v>
       </c>
       <c r="M25">
-        <v>4.1625262</v>
+        <v>4.3435056</v>
       </c>
       <c r="N25">
-        <v>166.2474738</v>
+        <v>166.0664944</v>
       </c>
       <c r="O25">
-        <v>20.780934225</v>
+        <v>20.7583118</v>
       </c>
       <c r="P25">
-        <v>145.466539575</v>
+        <v>145.3081826</v>
       </c>
       <c r="Q25">
-        <v>148.856539575</v>
+        <v>148.6981826</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1232421273005594</v>
+        <v>0.1241601231196746</v>
       </c>
       <c r="T25">
-        <v>1.30578552132095</v>
+        <v>1.321264249643863</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>40.93908165671126</v>
+        <v>39.23328658768162</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1049246935709527</v>
+        <v>0.1048300741204747</v>
       </c>
       <c r="C26">
-        <v>282.6671011886741</v>
+        <v>279.3116509468209</v>
       </c>
       <c r="D26">
-        <v>151.3191011886742</v>
+        <v>151.5616509468208</v>
       </c>
       <c r="E26">
-        <v>-19.848</v>
+        <v>-16.25</v>
       </c>
       <c r="F26">
-        <v>86.352</v>
+        <v>89.95</v>
       </c>
       <c r="G26">
         <v>217.7</v>
@@ -3419,28 +3419,28 @@
         <v>170.41</v>
       </c>
       <c r="M26">
-        <v>4.3435056</v>
+        <v>4.524485</v>
       </c>
       <c r="N26">
-        <v>166.0664944</v>
+        <v>165.885515</v>
       </c>
       <c r="O26">
-        <v>20.7583118</v>
+        <v>20.735689375</v>
       </c>
       <c r="P26">
-        <v>145.3081826</v>
+        <v>145.149825625</v>
       </c>
       <c r="Q26">
-        <v>148.6981826</v>
+        <v>148.539825625</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1241601231196746</v>
+        <v>0.1251025988272996</v>
       </c>
       <c r="T26">
-        <v>1.321264249643863</v>
+        <v>1.337155744055387</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>39.23328658768162</v>
+        <v>37.66395512417436</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1048300741204747</v>
+        <v>0.1047354546699966</v>
       </c>
       <c r="C27">
-        <v>279.3116509468209</v>
+        <v>275.9569795205365</v>
       </c>
       <c r="D27">
-        <v>151.5616509468208</v>
+        <v>151.8049795205365</v>
       </c>
       <c r="E27">
-        <v>-16.25</v>
+        <v>-12.652</v>
       </c>
       <c r="F27">
-        <v>89.95</v>
+        <v>93.548</v>
       </c>
       <c r="G27">
         <v>217.7</v>
@@ -3501,28 +3501,28 @@
         <v>170.41</v>
       </c>
       <c r="M27">
-        <v>4.524485</v>
+        <v>4.705464399999999</v>
       </c>
       <c r="N27">
-        <v>165.885515</v>
+        <v>165.7045356</v>
       </c>
       <c r="O27">
-        <v>20.735689375</v>
+        <v>20.71306695</v>
       </c>
       <c r="P27">
-        <v>145.149825625</v>
+        <v>144.99146865</v>
       </c>
       <c r="Q27">
-        <v>148.539825625</v>
+        <v>148.38146865</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1251025988272996</v>
+        <v>0.1260705468513468</v>
       </c>
       <c r="T27">
-        <v>1.337155744055387</v>
+        <v>1.353476738315872</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>37.66395512417436</v>
+        <v>36.21534146555227</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1047354546699966</v>
+        <v>0.1046408352195186</v>
       </c>
       <c r="C28">
-        <v>275.9569795205365</v>
+        <v>272.6030906669618</v>
       </c>
       <c r="D28">
-        <v>151.8049795205365</v>
+        <v>152.0490906669618</v>
       </c>
       <c r="E28">
-        <v>-12.652</v>
+        <v>-9.053999999999988</v>
       </c>
       <c r="F28">
-        <v>93.548</v>
+        <v>97.14600000000002</v>
       </c>
       <c r="G28">
         <v>217.7</v>
@@ -3583,28 +3583,28 @@
         <v>170.41</v>
       </c>
       <c r="M28">
-        <v>4.705464399999999</v>
+        <v>4.8864438</v>
       </c>
       <c r="N28">
-        <v>165.7045356</v>
+        <v>165.5235562</v>
       </c>
       <c r="O28">
-        <v>20.71306695</v>
+        <v>20.690444525</v>
       </c>
       <c r="P28">
-        <v>144.99146865</v>
+        <v>144.833111675</v>
       </c>
       <c r="Q28">
-        <v>148.38146865</v>
+        <v>148.223111675</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1260705468513468</v>
+        <v>0.1270650139993406</v>
       </c>
       <c r="T28">
-        <v>1.353476738315872</v>
+        <v>1.370244883104041</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>36.21534146555227</v>
+        <v>34.87403252238366</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1046408352195186</v>
+        <v>0.1045462157690406</v>
       </c>
       <c r="C29">
-        <v>272.6030906669618</v>
+        <v>269.2499881674435</v>
       </c>
       <c r="D29">
-        <v>152.0490906669618</v>
+        <v>152.2939881674435</v>
       </c>
       <c r="E29">
-        <v>-9.053999999999988</v>
+        <v>-5.455999999999989</v>
       </c>
       <c r="F29">
-        <v>97.14600000000002</v>
+        <v>100.744</v>
       </c>
       <c r="G29">
         <v>217.7</v>
@@ -3665,28 +3665,28 @@
         <v>170.41</v>
       </c>
       <c r="M29">
-        <v>4.8864438</v>
+        <v>5.0674232</v>
       </c>
       <c r="N29">
-        <v>165.5235562</v>
+        <v>165.3425768</v>
       </c>
       <c r="O29">
-        <v>20.690444525</v>
+        <v>20.6678221</v>
       </c>
       <c r="P29">
-        <v>144.833111675</v>
+        <v>144.6747547</v>
       </c>
       <c r="Q29">
-        <v>148.223111675</v>
+        <v>148.0647547</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1270650139993406</v>
+        <v>0.1280871052347786</v>
       </c>
       <c r="T29">
-        <v>1.370244883104041</v>
+        <v>1.387478809691881</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>34.87403252238366</v>
+        <v>33.62853136086996</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1045462157690406</v>
+        <v>0.1044515963185626</v>
       </c>
       <c r="C30">
-        <v>269.2499881674435</v>
+        <v>265.8976758277288</v>
       </c>
       <c r="D30">
-        <v>152.2939881674435</v>
+        <v>152.5396758277288</v>
       </c>
       <c r="E30">
-        <v>-5.455999999999989</v>
+        <v>-1.85799999999999</v>
       </c>
       <c r="F30">
-        <v>100.744</v>
+        <v>104.342</v>
       </c>
       <c r="G30">
         <v>217.7</v>
@@ -3747,28 +3747,28 @@
         <v>170.41</v>
       </c>
       <c r="M30">
-        <v>5.0674232</v>
+        <v>5.2484026</v>
       </c>
       <c r="N30">
-        <v>165.3425768</v>
+        <v>165.1615974</v>
       </c>
       <c r="O30">
-        <v>20.6678221</v>
+        <v>20.645199675</v>
       </c>
       <c r="P30">
-        <v>144.6747547</v>
+        <v>144.516397725</v>
       </c>
       <c r="Q30">
-        <v>148.0647547</v>
+        <v>147.906397725</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1280871052347786</v>
+        <v>0.1291379877726233</v>
       </c>
       <c r="T30">
-        <v>1.387478809691881</v>
+        <v>1.405198199000505</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>33.62853136086996</v>
+        <v>32.46892683118479</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1044515963185625</v>
+        <v>0.1043569768680845</v>
       </c>
       <c r="C31">
-        <v>265.8976758277289</v>
+        <v>262.5461574781637</v>
       </c>
       <c r="D31">
-        <v>152.5396758277289</v>
+        <v>152.7861574781637</v>
       </c>
       <c r="E31">
-        <v>-1.858000000000004</v>
+        <v>1.739999999999995</v>
       </c>
       <c r="F31">
-        <v>104.342</v>
+        <v>107.94</v>
       </c>
       <c r="G31">
         <v>217.7</v>
@@ -3829,28 +3829,28 @@
         <v>170.41</v>
       </c>
       <c r="M31">
-        <v>5.248402599999999</v>
+        <v>5.429381999999999</v>
       </c>
       <c r="N31">
-        <v>165.1615974</v>
+        <v>164.980618</v>
       </c>
       <c r="O31">
-        <v>20.645199675</v>
+        <v>20.62257725</v>
       </c>
       <c r="P31">
-        <v>144.516397725</v>
+        <v>144.35804075</v>
       </c>
       <c r="Q31">
-        <v>147.906397725</v>
+        <v>147.74804075</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1291379877726233</v>
+        <v>0.130218895525835</v>
       </c>
       <c r="T31">
-        <v>1.405198199000505</v>
+        <v>1.42342385657509</v>
       </c>
       <c r="U31">
         <v>0.0503</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>32.4689268311848</v>
+        <v>31.3866292701453</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1043569768680845</v>
+        <v>0.1042623574176065</v>
       </c>
       <c r="C32">
-        <v>262.5461574781637</v>
+        <v>259.1954369738905</v>
       </c>
       <c r="D32">
-        <v>152.7861574781637</v>
+        <v>153.0334369738905</v>
       </c>
       <c r="E32">
-        <v>1.739999999999995</v>
+        <v>5.337999999999994</v>
       </c>
       <c r="F32">
-        <v>107.94</v>
+        <v>111.538</v>
       </c>
       <c r="G32">
         <v>217.7</v>
@@ -3911,28 +3911,28 @@
         <v>170.41</v>
       </c>
       <c r="M32">
-        <v>5.429381999999999</v>
+        <v>5.610361399999999</v>
       </c>
       <c r="N32">
-        <v>164.980618</v>
+        <v>164.7996386</v>
       </c>
       <c r="O32">
-        <v>20.62257725</v>
+        <v>20.599954825</v>
       </c>
       <c r="P32">
-        <v>144.35804075</v>
+        <v>144.199683775</v>
       </c>
       <c r="Q32">
-        <v>147.74804075</v>
+        <v>147.589683775</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.130218895525835</v>
+        <v>0.1313311339385601</v>
       </c>
       <c r="T32">
-        <v>1.42342385657509</v>
+        <v>1.442177794079373</v>
       </c>
       <c r="U32">
         <v>0.0503</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>31.3866292701453</v>
+        <v>30.37415735820513</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1042623574176065</v>
+        <v>0.1041677379671284</v>
       </c>
       <c r="C33">
-        <v>259.1954369738905</v>
+        <v>255.8455181950506</v>
       </c>
       <c r="D33">
-        <v>153.0334369738905</v>
+        <v>153.2815181950506</v>
       </c>
       <c r="E33">
-        <v>5.337999999999994</v>
+        <v>8.936000000000007</v>
       </c>
       <c r="F33">
-        <v>111.538</v>
+        <v>115.136</v>
       </c>
       <c r="G33">
         <v>217.7</v>
@@ -3993,28 +3993,28 @@
         <v>170.41</v>
       </c>
       <c r="M33">
-        <v>5.610361399999999</v>
+        <v>5.7913408</v>
       </c>
       <c r="N33">
-        <v>164.7996386</v>
+        <v>164.6186592</v>
       </c>
       <c r="O33">
-        <v>20.599954825</v>
+        <v>20.5773324</v>
       </c>
       <c r="P33">
-        <v>144.199683775</v>
+        <v>144.0413268</v>
       </c>
       <c r="Q33">
-        <v>147.589683775</v>
+        <v>147.4313268</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1313311339385601</v>
+        <v>0.1324760852457771</v>
       </c>
       <c r="T33">
-        <v>1.442177794079373</v>
+        <v>1.461483317980841</v>
       </c>
       <c r="U33">
         <v>0.0503</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>30.37415735820513</v>
+        <v>29.42496494076122</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1041677379671284</v>
+        <v>0.1040731185166504</v>
       </c>
       <c r="C34">
-        <v>255.8455181950506</v>
+        <v>252.4964050469858</v>
       </c>
       <c r="D34">
-        <v>153.2815181950506</v>
+        <v>153.5304050469857</v>
       </c>
       <c r="E34">
-        <v>8.936000000000007</v>
+        <v>12.53400000000001</v>
       </c>
       <c r="F34">
-        <v>115.136</v>
+        <v>118.734</v>
       </c>
       <c r="G34">
         <v>217.7</v>
@@ -4075,28 +4075,28 @@
         <v>170.41</v>
       </c>
       <c r="M34">
-        <v>5.7913408</v>
+        <v>5.9723202</v>
       </c>
       <c r="N34">
-        <v>164.6186592</v>
+        <v>164.4376798</v>
       </c>
       <c r="O34">
-        <v>20.5773324</v>
+        <v>20.554709975</v>
       </c>
       <c r="P34">
-        <v>144.0413268</v>
+        <v>143.882969825</v>
       </c>
       <c r="Q34">
-        <v>147.4313268</v>
+        <v>147.272969825</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1324760852457771</v>
+        <v>0.1336552142039559</v>
       </c>
       <c r="T34">
-        <v>1.461483317980841</v>
+        <v>1.481365126177875</v>
       </c>
       <c r="U34">
         <v>0.0503</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>29.42496494076122</v>
+        <v>28.53329933649572</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1040731185166504</v>
+        <v>0.1039784990661724</v>
       </c>
       <c r="C35">
-        <v>252.4964050469858</v>
+        <v>249.1481014604442</v>
       </c>
       <c r="D35">
-        <v>153.5304050469857</v>
+        <v>153.7801014604442</v>
       </c>
       <c r="E35">
-        <v>12.53400000000001</v>
+        <v>16.13200000000001</v>
       </c>
       <c r="F35">
-        <v>118.734</v>
+        <v>122.332</v>
       </c>
       <c r="G35">
         <v>217.7</v>
@@ -4157,28 +4157,28 @@
         <v>170.41</v>
       </c>
       <c r="M35">
-        <v>5.9723202</v>
+        <v>6.1532996</v>
       </c>
       <c r="N35">
-        <v>164.4376798</v>
+        <v>164.2567004</v>
       </c>
       <c r="O35">
-        <v>20.554709975</v>
+        <v>20.53208755</v>
       </c>
       <c r="P35">
-        <v>143.882969825</v>
+        <v>143.72461285</v>
       </c>
       <c r="Q35">
-        <v>147.272969825</v>
+        <v>147.11461285</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1336552142039559</v>
+        <v>0.1348700743426854</v>
       </c>
       <c r="T35">
-        <v>1.481365126177875</v>
+        <v>1.501849413411183</v>
       </c>
       <c r="U35">
         <v>0.0503</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>28.53329933649572</v>
+        <v>27.6940846501282</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1039784990661724</v>
+        <v>0.1038838796156944</v>
       </c>
       <c r="C36">
-        <v>249.1481014604442</v>
+        <v>245.8006113917868</v>
       </c>
       <c r="D36">
-        <v>153.7801014604442</v>
+        <v>154.0306113917868</v>
       </c>
       <c r="E36">
-        <v>16.13200000000001</v>
+        <v>19.73000000000002</v>
       </c>
       <c r="F36">
-        <v>122.332</v>
+        <v>125.93</v>
       </c>
       <c r="G36">
         <v>217.7</v>
@@ -4239,28 +4239,28 @@
         <v>170.41</v>
       </c>
       <c r="M36">
-        <v>6.1532996</v>
+        <v>6.334279</v>
       </c>
       <c r="N36">
-        <v>164.2567004</v>
+        <v>164.075721</v>
       </c>
       <c r="O36">
-        <v>20.53208755</v>
+        <v>20.509465125</v>
       </c>
       <c r="P36">
-        <v>143.72461285</v>
+        <v>143.566255875</v>
       </c>
       <c r="Q36">
-        <v>147.11461285</v>
+        <v>146.956255875</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1348700743426854</v>
+        <v>0.1361223147933759</v>
       </c>
       <c r="T36">
-        <v>1.501849413411183</v>
+        <v>1.522963986405516</v>
       </c>
       <c r="U36">
         <v>0.0503</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>27.6940846501282</v>
+        <v>26.90282508869597</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1038838796156944</v>
+        <v>0.1037892601652163</v>
       </c>
       <c r="C37">
-        <v>245.8006113917868</v>
+        <v>242.4539388231967</v>
       </c>
       <c r="D37">
-        <v>154.0306113917868</v>
+        <v>154.2819388231968</v>
       </c>
       <c r="E37">
-        <v>19.73000000000002</v>
+        <v>23.32800000000002</v>
       </c>
       <c r="F37">
-        <v>125.93</v>
+        <v>129.528</v>
       </c>
       <c r="G37">
         <v>217.7</v>
@@ -4321,28 +4321,28 @@
         <v>170.41</v>
       </c>
       <c r="M37">
-        <v>6.334279</v>
+        <v>6.5152584</v>
       </c>
       <c r="N37">
-        <v>164.075721</v>
+        <v>163.8947416</v>
       </c>
       <c r="O37">
-        <v>20.509465125</v>
+        <v>20.4868427</v>
       </c>
       <c r="P37">
-        <v>143.566255875</v>
+        <v>143.4078989</v>
       </c>
       <c r="Q37">
-        <v>146.956255875</v>
+        <v>146.7978989</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1361223147933759</v>
+        <v>0.1374136877581505</v>
       </c>
       <c r="T37">
-        <v>1.522963986405516</v>
+        <v>1.544738389805921</v>
       </c>
       <c r="U37">
         <v>0.0503</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>26.90282508869597</v>
+        <v>26.15552439178775</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1037892601652163</v>
+        <v>0.1036946407147383</v>
       </c>
       <c r="C38">
-        <v>242.4539388231968</v>
+        <v>239.1080877628899</v>
       </c>
       <c r="D38">
-        <v>154.2819388231967</v>
+        <v>154.5340877628899</v>
       </c>
       <c r="E38">
-        <v>23.32799999999999</v>
+        <v>26.926</v>
       </c>
       <c r="F38">
-        <v>129.528</v>
+        <v>133.126</v>
       </c>
       <c r="G38">
         <v>217.7</v>
@@ -4403,28 +4403,28 @@
         <v>170.41</v>
       </c>
       <c r="M38">
-        <v>6.5152584</v>
+        <v>6.6962378</v>
       </c>
       <c r="N38">
-        <v>163.8947416</v>
+        <v>163.7137622</v>
       </c>
       <c r="O38">
-        <v>20.4868427</v>
+        <v>20.464220275</v>
       </c>
       <c r="P38">
-        <v>143.4078989</v>
+        <v>143.249541925</v>
       </c>
       <c r="Q38">
-        <v>146.7978989</v>
+        <v>146.639541925</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1374136877581505</v>
+        <v>0.1387460566900608</v>
       </c>
       <c r="T38">
-        <v>1.544738389805921</v>
+        <v>1.567204044107927</v>
       </c>
       <c r="U38">
         <v>0.0503</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>26.15552439178775</v>
+        <v>25.44861832714484</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1036946407147383</v>
+        <v>0.1036000212642603</v>
       </c>
       <c r="C39">
-        <v>239.1080877628899</v>
+        <v>235.7630622453281</v>
       </c>
       <c r="D39">
-        <v>154.5340877628899</v>
+        <v>154.7870622453282</v>
       </c>
       <c r="E39">
-        <v>26.926</v>
+        <v>30.52400000000002</v>
       </c>
       <c r="F39">
-        <v>133.126</v>
+        <v>136.724</v>
       </c>
       <c r="G39">
         <v>217.7</v>
@@ -4485,28 +4485,28 @@
         <v>170.41</v>
       </c>
       <c r="M39">
-        <v>6.6962378</v>
+        <v>6.8772172</v>
       </c>
       <c r="N39">
-        <v>163.7137622</v>
+        <v>163.5327828</v>
       </c>
       <c r="O39">
-        <v>20.464220275</v>
+        <v>20.44159785</v>
       </c>
       <c r="P39">
-        <v>143.249541925</v>
+        <v>143.09118495</v>
       </c>
       <c r="Q39">
-        <v>146.639541925</v>
+        <v>146.48118495</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1387460566900608</v>
+        <v>0.1401214052649359</v>
       </c>
       <c r="T39">
-        <v>1.567204044107927</v>
+        <v>1.590394396935804</v>
       </c>
       <c r="U39">
         <v>0.0503</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>25.44861832714484</v>
+        <v>24.77891784485155</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1036000212642603</v>
+        <v>0.1035054018137822</v>
       </c>
       <c r="C40">
-        <v>235.7630622453281</v>
+        <v>232.4188663314348</v>
       </c>
       <c r="D40">
-        <v>154.7870622453282</v>
+        <v>155.0408663314348</v>
       </c>
       <c r="E40">
-        <v>30.52400000000002</v>
+        <v>34.122</v>
       </c>
       <c r="F40">
-        <v>136.724</v>
+        <v>140.322</v>
       </c>
       <c r="G40">
         <v>217.7</v>
@@ -4567,28 +4567,28 @@
         <v>170.41</v>
       </c>
       <c r="M40">
-        <v>6.8772172</v>
+        <v>7.0581966</v>
       </c>
       <c r="N40">
-        <v>163.5327828</v>
+        <v>163.3518034</v>
       </c>
       <c r="O40">
-        <v>20.44159785</v>
+        <v>20.418975425</v>
       </c>
       <c r="P40">
-        <v>143.09118495</v>
+        <v>142.932827975</v>
       </c>
       <c r="Q40">
-        <v>146.48118495</v>
+        <v>146.322827975</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1401214052649359</v>
+        <v>0.1415418472357086</v>
       </c>
       <c r="T40">
-        <v>1.590394396935804</v>
+        <v>1.614345089200661</v>
       </c>
       <c r="U40">
         <v>0.0503</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>24.77891784485155</v>
+        <v>24.14356097703484</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1035054018137822</v>
+        <v>0.1034107823633042</v>
       </c>
       <c r="C41">
-        <v>232.4188663314348</v>
+        <v>229.0755041088113</v>
       </c>
       <c r="D41">
-        <v>155.0408663314348</v>
+        <v>155.2955041088114</v>
       </c>
       <c r="E41">
-        <v>34.122</v>
+        <v>37.72000000000001</v>
       </c>
       <c r="F41">
-        <v>140.322</v>
+        <v>143.92</v>
       </c>
       <c r="G41">
         <v>217.7</v>
@@ -4649,28 +4649,28 @@
         <v>170.41</v>
       </c>
       <c r="M41">
-        <v>7.0581966</v>
+        <v>7.239176</v>
       </c>
       <c r="N41">
-        <v>163.3518034</v>
+        <v>163.170824</v>
       </c>
       <c r="O41">
-        <v>20.418975425</v>
+        <v>20.396353</v>
       </c>
       <c r="P41">
-        <v>142.932827975</v>
+        <v>142.774471</v>
       </c>
       <c r="Q41">
-        <v>146.322827975</v>
+        <v>146.164471</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1415418472357086</v>
+        <v>0.1430096372721737</v>
       </c>
       <c r="T41">
-        <v>1.614345089200661</v>
+        <v>1.639094137874346</v>
       </c>
       <c r="U41">
         <v>0.0503</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>24.14356097703484</v>
+        <v>23.53997195260898</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1034107823633042</v>
+        <v>0.1033161629128262</v>
       </c>
       <c r="C42">
-        <v>229.0755041088113</v>
+        <v>225.7329796919576</v>
       </c>
       <c r="D42">
-        <v>155.2955041088114</v>
+        <v>155.5509796919576</v>
       </c>
       <c r="E42">
-        <v>37.72000000000001</v>
+        <v>41.31800000000003</v>
       </c>
       <c r="F42">
-        <v>143.92</v>
+        <v>147.518</v>
       </c>
       <c r="G42">
         <v>217.7</v>
@@ -4731,28 +4731,28 @@
         <v>170.41</v>
       </c>
       <c r="M42">
-        <v>7.239176</v>
+        <v>7.420155400000001</v>
       </c>
       <c r="N42">
-        <v>163.170824</v>
+        <v>162.9898446</v>
       </c>
       <c r="O42">
-        <v>20.396353</v>
+        <v>20.373730575</v>
       </c>
       <c r="P42">
-        <v>142.774471</v>
+        <v>142.616114025</v>
       </c>
       <c r="Q42">
-        <v>146.164471</v>
+        <v>146.006114025</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1430096372721737</v>
+        <v>0.1445271829030952</v>
       </c>
       <c r="T42">
-        <v>1.639094137874346</v>
+        <v>1.664682137350529</v>
       </c>
       <c r="U42">
         <v>0.0503</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>23.53997195260898</v>
+        <v>22.96582629522826</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1033161629128262</v>
+        <v>0.1032215434623482</v>
       </c>
       <c r="C43">
-        <v>225.7329796919576</v>
+        <v>222.3912972224924</v>
       </c>
       <c r="D43">
-        <v>155.5509796919576</v>
+        <v>155.8072972224924</v>
       </c>
       <c r="E43">
-        <v>41.31800000000003</v>
+        <v>44.91600000000001</v>
       </c>
       <c r="F43">
-        <v>147.518</v>
+        <v>151.116</v>
       </c>
       <c r="G43">
         <v>217.7</v>
@@ -4813,28 +4813,28 @@
         <v>170.41</v>
       </c>
       <c r="M43">
-        <v>7.420155400000001</v>
+        <v>7.601134800000001</v>
       </c>
       <c r="N43">
-        <v>162.9898446</v>
+        <v>162.8088652</v>
       </c>
       <c r="O43">
-        <v>20.373730575</v>
+        <v>20.35110815</v>
       </c>
       <c r="P43">
-        <v>142.616114025</v>
+        <v>142.45775705</v>
       </c>
       <c r="Q43">
-        <v>146.006114025</v>
+        <v>145.84775705</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1445271829030952</v>
+        <v>0.1460970576937037</v>
       </c>
       <c r="T43">
-        <v>1.664682137350529</v>
+        <v>1.691152481636236</v>
       </c>
       <c r="U43">
         <v>0.0503</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>22.96582629522826</v>
+        <v>22.41902090724664</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1032215434623481</v>
+        <v>0.1031269240118701</v>
       </c>
       <c r="C44">
-        <v>222.3912972224924</v>
+        <v>219.0504608693786</v>
       </c>
       <c r="D44">
-        <v>155.8072972224924</v>
+        <v>156.0644608693786</v>
       </c>
       <c r="E44">
-        <v>44.91599999999998</v>
+        <v>48.514</v>
       </c>
       <c r="F44">
-        <v>151.116</v>
+        <v>154.714</v>
       </c>
       <c r="G44">
         <v>217.7</v>
@@ -4895,28 +4895,28 @@
         <v>170.41</v>
       </c>
       <c r="M44">
-        <v>7.601134799999999</v>
+        <v>7.7821142</v>
       </c>
       <c r="N44">
-        <v>162.8088652</v>
+        <v>162.6278858</v>
       </c>
       <c r="O44">
-        <v>20.35110815</v>
+        <v>20.328485725</v>
       </c>
       <c r="P44">
-        <v>142.45775705</v>
+        <v>142.299400075</v>
       </c>
       <c r="Q44">
-        <v>145.84775705</v>
+        <v>145.689400075</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1460970576937037</v>
+        <v>0.1477220158102984</v>
       </c>
       <c r="T44">
-        <v>1.691152481636235</v>
+        <v>1.718551609931966</v>
       </c>
       <c r="U44">
         <v>0.0503</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>22.41902090724664</v>
+        <v>21.89764832800835</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1031269240118701</v>
+        <v>0.1030323045613921</v>
       </c>
       <c r="C45">
-        <v>219.0504608693786</v>
+        <v>215.710474829148</v>
       </c>
       <c r="D45">
-        <v>156.0644608693786</v>
+        <v>156.322474829148</v>
       </c>
       <c r="E45">
-        <v>48.514</v>
+        <v>52.11200000000001</v>
       </c>
       <c r="F45">
-        <v>154.714</v>
+        <v>158.312</v>
       </c>
       <c r="G45">
         <v>217.7</v>
@@ -4977,28 +4977,28 @@
         <v>170.41</v>
       </c>
       <c r="M45">
-        <v>7.7821142</v>
+        <v>7.963093600000001</v>
       </c>
       <c r="N45">
-        <v>162.6278858</v>
+        <v>162.4469064</v>
       </c>
       <c r="O45">
-        <v>20.328485725</v>
+        <v>20.3058633</v>
       </c>
       <c r="P45">
-        <v>142.299400075</v>
+        <v>142.1410431</v>
       </c>
       <c r="Q45">
-        <v>145.689400075</v>
+        <v>145.5310431</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1477220158102984</v>
+        <v>0.149405008145343</v>
       </c>
       <c r="T45">
-        <v>1.718551609931966</v>
+        <v>1.746929278523974</v>
       </c>
       <c r="U45">
         <v>0.0503</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>21.89764832800835</v>
+        <v>21.39997450237179</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1030323045613921</v>
+        <v>0.1029376851109141</v>
       </c>
       <c r="C46">
-        <v>215.710474829148</v>
+        <v>212.3713433261301</v>
       </c>
       <c r="D46">
-        <v>156.322474829148</v>
+        <v>156.5813433261301</v>
       </c>
       <c r="E46">
-        <v>52.11200000000001</v>
+        <v>55.70999999999999</v>
       </c>
       <c r="F46">
-        <v>158.312</v>
+        <v>161.91</v>
       </c>
       <c r="G46">
         <v>217.7</v>
@@ -5059,28 +5059,28 @@
         <v>170.41</v>
       </c>
       <c r="M46">
-        <v>7.963093600000001</v>
+        <v>8.144072999999999</v>
       </c>
       <c r="N46">
-        <v>162.4469064</v>
+        <v>162.265927</v>
       </c>
       <c r="O46">
-        <v>20.3058633</v>
+        <v>20.283240875</v>
       </c>
       <c r="P46">
-        <v>142.1410431</v>
+        <v>141.982686125</v>
       </c>
       <c r="Q46">
-        <v>145.5310431</v>
+        <v>145.372686125</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.149405008145343</v>
+        <v>0.1511492002016619</v>
       </c>
       <c r="T46">
-        <v>1.746929278523974</v>
+        <v>1.776338862337509</v>
       </c>
       <c r="U46">
         <v>0.0503</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>21.39997450237179</v>
+        <v>20.9244195134302</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1029376851109141</v>
+        <v>0.102843065660436</v>
       </c>
       <c r="C47">
-        <v>212.3713433261301</v>
+        <v>209.0330706126828</v>
       </c>
       <c r="D47">
-        <v>156.5813433261301</v>
+        <v>156.8410706126828</v>
       </c>
       <c r="E47">
-        <v>55.70999999999999</v>
+        <v>59.30800000000001</v>
       </c>
       <c r="F47">
-        <v>161.91</v>
+        <v>165.508</v>
       </c>
       <c r="G47">
         <v>217.7</v>
@@ -5141,28 +5141,28 @@
         <v>170.41</v>
       </c>
       <c r="M47">
-        <v>8.144072999999999</v>
+        <v>8.325052400000001</v>
       </c>
       <c r="N47">
-        <v>162.265927</v>
+        <v>162.0849476</v>
       </c>
       <c r="O47">
-        <v>20.283240875</v>
+        <v>20.26061845</v>
       </c>
       <c r="P47">
-        <v>141.982686125</v>
+        <v>141.82432915</v>
       </c>
       <c r="Q47">
-        <v>145.372686125</v>
+        <v>145.21432915</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1511492002016619</v>
+        <v>0.1529579919637704</v>
       </c>
       <c r="T47">
-        <v>1.776338862337509</v>
+        <v>1.806837689995989</v>
       </c>
       <c r="U47">
         <v>0.0503</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>20.9244195134302</v>
+        <v>20.46954082835563</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.102843065660436</v>
+        <v>0.102748446209958</v>
       </c>
       <c r="C48">
-        <v>209.0330706126828</v>
+        <v>205.6956609694248</v>
       </c>
       <c r="D48">
-        <v>156.8410706126828</v>
+        <v>157.1016609694248</v>
       </c>
       <c r="E48">
-        <v>59.30800000000001</v>
+        <v>62.90600000000002</v>
       </c>
       <c r="F48">
-        <v>165.508</v>
+        <v>169.106</v>
       </c>
       <c r="G48">
         <v>217.7</v>
@@ -5223,28 +5223,28 @@
         <v>170.41</v>
       </c>
       <c r="M48">
-        <v>8.325052400000001</v>
+        <v>8.506031800000001</v>
       </c>
       <c r="N48">
-        <v>162.0849476</v>
+        <v>161.9039682</v>
       </c>
       <c r="O48">
-        <v>20.26061845</v>
+        <v>20.237996025</v>
       </c>
       <c r="P48">
-        <v>141.82432915</v>
+        <v>141.665972175</v>
       </c>
       <c r="Q48">
-        <v>145.21432915</v>
+        <v>145.055972175</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1529579919637704</v>
+        <v>0.1548350400187886</v>
       </c>
       <c r="T48">
-        <v>1.806837689995989</v>
+        <v>1.838487416811394</v>
       </c>
       <c r="U48">
         <v>0.0503</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>20.46954082835563</v>
+        <v>20.03401868307147</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.102748446209958</v>
+        <v>0.10265382675948</v>
       </c>
       <c r="C49">
-        <v>205.6956609694248</v>
+        <v>202.3591187054713</v>
       </c>
       <c r="D49">
-        <v>157.1016609694248</v>
+        <v>157.3631187054713</v>
       </c>
       <c r="E49">
-        <v>62.90600000000002</v>
+        <v>66.504</v>
       </c>
       <c r="F49">
-        <v>169.106</v>
+        <v>172.704</v>
       </c>
       <c r="G49">
         <v>217.7</v>
@@ -5305,28 +5305,28 @@
         <v>170.41</v>
       </c>
       <c r="M49">
-        <v>8.506031800000001</v>
+        <v>8.687011200000001</v>
       </c>
       <c r="N49">
-        <v>161.9039682</v>
+        <v>161.7229888</v>
       </c>
       <c r="O49">
-        <v>20.237996025</v>
+        <v>20.2153736</v>
       </c>
       <c r="P49">
-        <v>141.665972175</v>
+        <v>141.5076152</v>
       </c>
       <c r="Q49">
-        <v>145.055972175</v>
+        <v>144.8976152</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1548350400187886</v>
+        <v>0.1567842822297691</v>
       </c>
       <c r="T49">
-        <v>1.838487416811394</v>
+        <v>1.871354440812006</v>
       </c>
       <c r="U49">
         <v>0.0503</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>20.03401868307147</v>
+        <v>19.61664329384081</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.10265382675948</v>
+        <v>0.1025592073090019</v>
       </c>
       <c r="C50">
-        <v>202.3591187054713</v>
+        <v>199.0234481586711</v>
       </c>
       <c r="D50">
-        <v>157.3631187054713</v>
+        <v>157.6254481586711</v>
       </c>
       <c r="E50">
-        <v>66.504</v>
+        <v>70.10199999999999</v>
       </c>
       <c r="F50">
-        <v>172.704</v>
+        <v>176.302</v>
       </c>
       <c r="G50">
         <v>217.7</v>
@@ -5387,28 +5387,28 @@
         <v>170.41</v>
       </c>
       <c r="M50">
-        <v>8.687011200000001</v>
+        <v>8.867990599999999</v>
       </c>
       <c r="N50">
-        <v>161.7229888</v>
+        <v>161.5420094</v>
       </c>
       <c r="O50">
-        <v>20.2153736</v>
+        <v>20.19275117500001</v>
       </c>
       <c r="P50">
-        <v>141.5076152</v>
+        <v>141.349258225</v>
       </c>
       <c r="Q50">
-        <v>144.8976152</v>
+        <v>144.739258225</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1567842822297691</v>
+        <v>0.1588099653117684</v>
       </c>
       <c r="T50">
-        <v>1.871354440812006</v>
+        <v>1.905510367714603</v>
       </c>
       <c r="U50">
         <v>0.0503</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>19.61664329384081</v>
+        <v>19.21630363478284</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1025592073090019</v>
+        <v>0.1024645878585239</v>
       </c>
       <c r="C51">
-        <v>199.0234481586711</v>
+        <v>195.6886536958465</v>
       </c>
       <c r="D51">
-        <v>157.6254481586711</v>
+        <v>157.8886536958465</v>
       </c>
       <c r="E51">
-        <v>70.10199999999999</v>
+        <v>73.7</v>
       </c>
       <c r="F51">
-        <v>176.302</v>
+        <v>179.9</v>
       </c>
       <c r="G51">
         <v>217.7</v>
@@ -5469,28 +5469,28 @@
         <v>170.41</v>
       </c>
       <c r="M51">
-        <v>8.867990599999999</v>
+        <v>9.048970000000001</v>
       </c>
       <c r="N51">
-        <v>161.5420094</v>
+        <v>161.36103</v>
       </c>
       <c r="O51">
-        <v>20.19275117500001</v>
+        <v>20.17012875</v>
       </c>
       <c r="P51">
-        <v>141.349258225</v>
+        <v>141.19090125</v>
       </c>
       <c r="Q51">
-        <v>144.739258225</v>
+        <v>144.58090125</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1588099653117684</v>
+        <v>0.1609166757170478</v>
       </c>
       <c r="T51">
-        <v>1.905510367714603</v>
+        <v>1.941032531693304</v>
       </c>
       <c r="U51">
         <v>0.0503</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>19.21630363478284</v>
+        <v>18.83197756208718</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1024645878585239</v>
+        <v>0.1023699684080459</v>
       </c>
       <c r="C52">
-        <v>195.6886536958465</v>
+        <v>192.354739713036</v>
       </c>
       <c r="D52">
-        <v>157.8886536958465</v>
+        <v>158.152739713036</v>
       </c>
       <c r="E52">
-        <v>73.7</v>
+        <v>77.29800000000002</v>
       </c>
       <c r="F52">
-        <v>179.9</v>
+        <v>183.498</v>
       </c>
       <c r="G52">
         <v>217.7</v>
@@ -5551,28 +5551,28 @@
         <v>170.41</v>
       </c>
       <c r="M52">
-        <v>9.048970000000001</v>
+        <v>9.229949400000001</v>
       </c>
       <c r="N52">
-        <v>161.36103</v>
+        <v>161.1800506</v>
       </c>
       <c r="O52">
-        <v>20.17012875</v>
+        <v>20.147506325</v>
       </c>
       <c r="P52">
-        <v>141.19090125</v>
+        <v>141.032544275</v>
       </c>
       <c r="Q52">
-        <v>144.58090125</v>
+        <v>144.422544275</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1609166757170478</v>
+        <v>0.1631093743021344</v>
       </c>
       <c r="T52">
-        <v>1.941032531693304</v>
+        <v>1.978004579916034</v>
       </c>
       <c r="U52">
         <v>0.0503</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>18.83197756208718</v>
+        <v>18.46272310008547</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1023699684080459</v>
+        <v>0.1022753489575678</v>
       </c>
       <c r="C53">
-        <v>192.354739713036</v>
+        <v>189.0217106357387</v>
       </c>
       <c r="D53">
-        <v>158.152739713036</v>
+        <v>158.4177106357387</v>
       </c>
       <c r="E53">
-        <v>77.29800000000002</v>
+        <v>80.896</v>
       </c>
       <c r="F53">
-        <v>183.498</v>
+        <v>187.096</v>
       </c>
       <c r="G53">
         <v>217.7</v>
@@ -5633,28 +5633,28 @@
         <v>170.41</v>
       </c>
       <c r="M53">
-        <v>9.229949400000001</v>
+        <v>9.410928799999999</v>
       </c>
       <c r="N53">
-        <v>161.1800506</v>
+        <v>160.9990712</v>
       </c>
       <c r="O53">
-        <v>20.147506325</v>
+        <v>20.1248839</v>
       </c>
       <c r="P53">
-        <v>141.032544275</v>
+        <v>140.8741873</v>
       </c>
       <c r="Q53">
-        <v>144.422544275</v>
+        <v>144.2641873</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1631093743021344</v>
+        <v>0.1653934353282663</v>
       </c>
       <c r="T53">
-        <v>1.978004579916034</v>
+        <v>2.016517130148044</v>
       </c>
       <c r="U53">
         <v>0.0503</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>18.46272310008547</v>
+        <v>18.10767073277614</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1022753489575678</v>
+        <v>0.1021807295070898</v>
       </c>
       <c r="C54">
-        <v>189.0217106357387</v>
+        <v>185.6895709191616</v>
       </c>
       <c r="D54">
-        <v>158.4177106357387</v>
+        <v>158.6835709191616</v>
       </c>
       <c r="E54">
-        <v>80.896</v>
+        <v>84.49400000000001</v>
       </c>
       <c r="F54">
-        <v>187.096</v>
+        <v>190.694</v>
       </c>
       <c r="G54">
         <v>217.7</v>
@@ -5715,28 +5715,28 @@
         <v>170.41</v>
       </c>
       <c r="M54">
-        <v>9.410928799999999</v>
+        <v>9.591908200000001</v>
       </c>
       <c r="N54">
-        <v>160.9990712</v>
+        <v>160.8180918</v>
       </c>
       <c r="O54">
-        <v>20.1248839</v>
+        <v>20.102261475</v>
       </c>
       <c r="P54">
-        <v>140.8741873</v>
+        <v>140.715830325</v>
       </c>
       <c r="Q54">
-        <v>144.2641873</v>
+        <v>144.105830325</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1653934353282663</v>
+        <v>0.1677746904406166</v>
       </c>
       <c r="T54">
-        <v>2.016517130148044</v>
+        <v>2.056668512304821</v>
       </c>
       <c r="U54">
         <v>0.0503</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>18.10767073277614</v>
+        <v>17.76601656800677</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1021807295070898</v>
+        <v>0.1020861100566118</v>
       </c>
       <c r="C55">
-        <v>185.6895709191616</v>
+        <v>182.3583250484691</v>
       </c>
       <c r="D55">
-        <v>158.6835709191616</v>
+        <v>158.9503250484691</v>
       </c>
       <c r="E55">
-        <v>84.49400000000001</v>
+        <v>88.09200000000003</v>
       </c>
       <c r="F55">
-        <v>190.694</v>
+        <v>194.292</v>
       </c>
       <c r="G55">
         <v>217.7</v>
@@ -5797,28 +5797,28 @@
         <v>170.41</v>
       </c>
       <c r="M55">
-        <v>9.591908200000001</v>
+        <v>9.772887600000001</v>
       </c>
       <c r="N55">
-        <v>160.8180918</v>
+        <v>160.6371124</v>
       </c>
       <c r="O55">
-        <v>20.102261475</v>
+        <v>20.07963905</v>
       </c>
       <c r="P55">
-        <v>140.715830325</v>
+        <v>140.55747335</v>
       </c>
       <c r="Q55">
-        <v>144.105830325</v>
+        <v>143.94747335</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1677746904406166</v>
+        <v>0.1702594783839386</v>
       </c>
       <c r="T55">
-        <v>2.056668512304821</v>
+        <v>2.098565606729283</v>
       </c>
       <c r="U55">
         <v>0.0503</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>17.76601656800677</v>
+        <v>17.43701626119183</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1020861100566118</v>
+        <v>0.1019914906061337</v>
       </c>
       <c r="C56">
-        <v>182.3583250484691</v>
+        <v>179.0279775390358</v>
       </c>
       <c r="D56">
-        <v>158.9503250484691</v>
+        <v>159.2179775390359</v>
       </c>
       <c r="E56">
-        <v>88.09200000000003</v>
+        <v>91.69000000000001</v>
       </c>
       <c r="F56">
-        <v>194.292</v>
+        <v>197.89</v>
       </c>
       <c r="G56">
         <v>217.7</v>
@@ -5879,28 +5879,28 @@
         <v>170.41</v>
       </c>
       <c r="M56">
-        <v>9.772887600000001</v>
+        <v>9.953867000000001</v>
       </c>
       <c r="N56">
-        <v>160.6371124</v>
+        <v>160.456133</v>
       </c>
       <c r="O56">
-        <v>20.07963905</v>
+        <v>20.057016625</v>
       </c>
       <c r="P56">
-        <v>140.55747335</v>
+        <v>140.399116375</v>
       </c>
       <c r="Q56">
-        <v>143.94747335</v>
+        <v>143.789116375</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1702594783839386</v>
+        <v>0.1728547013469638</v>
       </c>
       <c r="T56">
-        <v>2.098565606729283</v>
+        <v>2.142324794239277</v>
       </c>
       <c r="U56">
         <v>0.0503</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>17.43701626119183</v>
+        <v>17.11997960189743</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1019914906061337</v>
+        <v>0.1018968711556557</v>
       </c>
       <c r="C57">
-        <v>179.0279775390358</v>
+        <v>175.6985329367008</v>
       </c>
       <c r="D57">
-        <v>159.2179775390359</v>
+        <v>159.4865329367008</v>
       </c>
       <c r="E57">
-        <v>91.69000000000001</v>
+        <v>95.28800000000003</v>
       </c>
       <c r="F57">
-        <v>197.89</v>
+        <v>201.488</v>
       </c>
       <c r="G57">
         <v>217.7</v>
@@ -5961,28 +5961,28 @@
         <v>170.41</v>
       </c>
       <c r="M57">
-        <v>9.953867000000001</v>
+        <v>10.1348464</v>
       </c>
       <c r="N57">
-        <v>160.456133</v>
+        <v>160.2751536</v>
       </c>
       <c r="O57">
-        <v>20.057016625</v>
+        <v>20.0343942</v>
       </c>
       <c r="P57">
-        <v>140.399116375</v>
+        <v>140.2407594</v>
       </c>
       <c r="Q57">
-        <v>143.789116375</v>
+        <v>143.6307594</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1728547013469638</v>
+        <v>0.1755678889901266</v>
       </c>
       <c r="T57">
-        <v>2.142324794239277</v>
+        <v>2.188073035726998</v>
       </c>
       <c r="U57">
         <v>0.0503</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>17.11997960189743</v>
+        <v>16.81426568043498</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1018968711556557</v>
+        <v>0.1018022517051777</v>
       </c>
       <c r="C58">
-        <v>175.6985329367008</v>
+        <v>172.3699958180249</v>
       </c>
       <c r="D58">
-        <v>159.4865329367008</v>
+        <v>159.755995818025</v>
       </c>
       <c r="E58">
-        <v>95.28800000000003</v>
+        <v>98.88600000000004</v>
       </c>
       <c r="F58">
-        <v>201.488</v>
+        <v>205.086</v>
       </c>
       <c r="G58">
         <v>217.7</v>
@@ -6043,28 +6043,28 @@
         <v>170.41</v>
       </c>
       <c r="M58">
-        <v>10.1348464</v>
+        <v>10.3158258</v>
       </c>
       <c r="N58">
-        <v>160.2751536</v>
+        <v>160.0941742</v>
       </c>
       <c r="O58">
-        <v>20.0343942</v>
+        <v>20.011771775</v>
       </c>
       <c r="P58">
-        <v>140.2407594</v>
+        <v>140.082402425</v>
       </c>
       <c r="Q58">
-        <v>143.6307594</v>
+        <v>143.472402425</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1755678889901266</v>
+        <v>0.1784072714073899</v>
       </c>
       <c r="T58">
-        <v>2.188073035726998</v>
+        <v>2.235949102400194</v>
       </c>
       <c r="U58">
         <v>0.0503</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>16.81426568043498</v>
+        <v>16.51927856323437</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1018022517051777</v>
+        <v>0.1017076322546996</v>
       </c>
       <c r="C59">
-        <v>172.3699958180249</v>
+        <v>169.0423707905512</v>
       </c>
       <c r="D59">
-        <v>159.755995818025</v>
+        <v>160.0263707905513</v>
       </c>
       <c r="E59">
-        <v>98.88600000000004</v>
+        <v>102.484</v>
       </c>
       <c r="F59">
-        <v>205.086</v>
+        <v>208.684</v>
       </c>
       <c r="G59">
         <v>217.7</v>
@@ -6125,28 +6125,28 @@
         <v>170.41</v>
       </c>
       <c r="M59">
-        <v>10.3158258</v>
+        <v>10.4968052</v>
       </c>
       <c r="N59">
-        <v>160.0941742</v>
+        <v>159.9131948</v>
       </c>
       <c r="O59">
-        <v>20.011771775</v>
+        <v>19.98914935</v>
       </c>
       <c r="P59">
-        <v>140.082402425</v>
+        <v>139.92404545</v>
       </c>
       <c r="Q59">
-        <v>143.472402425</v>
+        <v>143.31404545</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1784072714073899</v>
+        <v>0.1813818625111896</v>
       </c>
       <c r="T59">
-        <v>2.235949102400194</v>
+        <v>2.286104981772115</v>
       </c>
       <c r="U59">
         <v>0.0503</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>16.51927856323437</v>
+        <v>16.23446341559239</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1017076322546996</v>
+        <v>0.1016130128042216</v>
       </c>
       <c r="C60">
-        <v>169.0423707905513</v>
+        <v>165.7156624930671</v>
       </c>
       <c r="D60">
-        <v>160.0263707905513</v>
+        <v>160.2976624930671</v>
       </c>
       <c r="E60">
-        <v>102.484</v>
+        <v>106.082</v>
       </c>
       <c r="F60">
-        <v>208.684</v>
+        <v>212.282</v>
       </c>
       <c r="G60">
         <v>217.7</v>
@@ -6207,28 +6207,28 @@
         <v>170.41</v>
       </c>
       <c r="M60">
-        <v>10.4968052</v>
+        <v>10.6777846</v>
       </c>
       <c r="N60">
-        <v>159.9131948</v>
+        <v>159.7322154</v>
       </c>
       <c r="O60">
-        <v>19.98914935</v>
+        <v>19.966526925</v>
       </c>
       <c r="P60">
-        <v>139.92404545</v>
+        <v>139.765688475</v>
       </c>
       <c r="Q60">
-        <v>143.31404545</v>
+        <v>143.155688475</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1813818625111896</v>
+        <v>0.1845015556200527</v>
       </c>
       <c r="T60">
-        <v>2.286104981772114</v>
+        <v>2.338707489406079</v>
       </c>
       <c r="U60">
         <v>0.0503</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>16.23446341559239</v>
+        <v>15.95930301871795</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1016130128042216</v>
+        <v>0.1015183933537436</v>
       </c>
       <c r="C61">
-        <v>165.7156624930671</v>
+        <v>162.3898755958698</v>
       </c>
       <c r="D61">
-        <v>160.2976624930671</v>
+        <v>160.5698755958698</v>
       </c>
       <c r="E61">
-        <v>106.082</v>
+        <v>109.68</v>
       </c>
       <c r="F61">
-        <v>212.282</v>
+        <v>215.88</v>
       </c>
       <c r="G61">
         <v>217.7</v>
@@ -6289,28 +6289,28 @@
         <v>170.41</v>
       </c>
       <c r="M61">
-        <v>10.6777846</v>
+        <v>10.858764</v>
       </c>
       <c r="N61">
-        <v>159.7322154</v>
+        <v>159.551236</v>
       </c>
       <c r="O61">
-        <v>19.966526925</v>
+        <v>19.9439045</v>
       </c>
       <c r="P61">
-        <v>139.765688475</v>
+        <v>139.6073315</v>
       </c>
       <c r="Q61">
-        <v>143.155688475</v>
+        <v>142.9973315</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1845015556200527</v>
+        <v>0.1877772333843589</v>
       </c>
       <c r="T61">
-        <v>2.338707489406079</v>
+        <v>2.393940122421742</v>
       </c>
       <c r="U61">
         <v>0.0503</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>15.95930301871795</v>
+        <v>15.69331463507265</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1015183933537436</v>
+        <v>0.1014237739032655</v>
       </c>
       <c r="C62">
-        <v>162.3898755958698</v>
+        <v>159.0650148010347</v>
       </c>
       <c r="D62">
-        <v>160.5698755958698</v>
+        <v>160.8430148010347</v>
       </c>
       <c r="E62">
-        <v>109.68</v>
+        <v>113.278</v>
       </c>
       <c r="F62">
-        <v>215.88</v>
+        <v>219.478</v>
       </c>
       <c r="G62">
         <v>217.7</v>
@@ -6371,28 +6371,28 @@
         <v>170.41</v>
       </c>
       <c r="M62">
-        <v>10.858764</v>
+        <v>11.0397434</v>
       </c>
       <c r="N62">
-        <v>159.551236</v>
+        <v>159.3702566</v>
       </c>
       <c r="O62">
-        <v>19.9439045</v>
+        <v>19.921282075</v>
       </c>
       <c r="P62">
-        <v>139.6073315</v>
+        <v>139.448974525</v>
       </c>
       <c r="Q62">
-        <v>142.9973315</v>
+        <v>142.838974525</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1877772333843589</v>
+        <v>0.1912208946237578</v>
       </c>
       <c r="T62">
-        <v>2.393940122421742</v>
+        <v>2.452005198156157</v>
       </c>
       <c r="U62">
         <v>0.0503</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>15.69331463507265</v>
+        <v>15.43604718203867</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1014237739032655</v>
+        <v>0.1013291544527875</v>
       </c>
       <c r="C63">
-        <v>159.0650148010347</v>
+        <v>155.7410848426854</v>
       </c>
       <c r="D63">
-        <v>160.8430148010347</v>
+        <v>161.1170848426854</v>
       </c>
       <c r="E63">
-        <v>113.278</v>
+        <v>116.876</v>
       </c>
       <c r="F63">
-        <v>219.478</v>
+        <v>223.076</v>
       </c>
       <c r="G63">
         <v>217.7</v>
@@ -6453,28 +6453,28 @@
         <v>170.41</v>
       </c>
       <c r="M63">
-        <v>11.0397434</v>
+        <v>11.2207228</v>
       </c>
       <c r="N63">
-        <v>159.3702566</v>
+        <v>159.1892772</v>
       </c>
       <c r="O63">
-        <v>19.921282075</v>
+        <v>19.89865965</v>
       </c>
       <c r="P63">
-        <v>139.448974525</v>
+        <v>139.29061755</v>
       </c>
       <c r="Q63">
-        <v>142.838974525</v>
+        <v>142.68061755</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1912208946237578</v>
+        <v>0.194845801191546</v>
       </c>
       <c r="T63">
-        <v>2.452005198156157</v>
+        <v>2.513126330508173</v>
       </c>
       <c r="U63">
         <v>0.0503</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>15.43604718203867</v>
+        <v>15.18707867910257</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1013291544527875</v>
+        <v>0.1012345350023095</v>
       </c>
       <c r="C64">
-        <v>155.7410848426854</v>
+        <v>152.4180904872678</v>
       </c>
       <c r="D64">
-        <v>161.1170848426854</v>
+        <v>161.3920904872679</v>
       </c>
       <c r="E64">
-        <v>116.876</v>
+        <v>120.474</v>
       </c>
       <c r="F64">
-        <v>223.076</v>
+        <v>226.674</v>
       </c>
       <c r="G64">
         <v>217.7</v>
@@ -6535,28 +6535,28 @@
         <v>170.41</v>
       </c>
       <c r="M64">
-        <v>11.2207228</v>
+        <v>11.4017022</v>
       </c>
       <c r="N64">
-        <v>159.1892772</v>
+        <v>159.0082978</v>
       </c>
       <c r="O64">
-        <v>19.89865965</v>
+        <v>19.876037225</v>
       </c>
       <c r="P64">
-        <v>139.29061755</v>
+        <v>139.132260575</v>
       </c>
       <c r="Q64">
-        <v>142.68061755</v>
+        <v>142.522260575</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.194845801191546</v>
+        <v>0.1986666486548904</v>
       </c>
       <c r="T64">
-        <v>2.513126330508173</v>
+        <v>2.57755130785219</v>
       </c>
       <c r="U64">
         <v>0.0503</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>15.18707867910257</v>
+        <v>14.94601393816443</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1012345350023095</v>
+        <v>0.1011399155518314</v>
       </c>
       <c r="C65">
-        <v>152.4180904872678</v>
+        <v>149.0960365338263</v>
       </c>
       <c r="D65">
-        <v>161.3920904872679</v>
+        <v>161.6680365338263</v>
       </c>
       <c r="E65">
-        <v>120.474</v>
+        <v>124.072</v>
       </c>
       <c r="F65">
-        <v>226.674</v>
+        <v>230.272</v>
       </c>
       <c r="G65">
         <v>217.7</v>
@@ -6617,28 +6617,28 @@
         <v>170.41</v>
       </c>
       <c r="M65">
-        <v>11.4017022</v>
+        <v>11.5826816</v>
       </c>
       <c r="N65">
-        <v>159.0082978</v>
+        <v>158.8273184</v>
       </c>
       <c r="O65">
-        <v>19.876037225</v>
+        <v>19.8534148</v>
       </c>
       <c r="P65">
-        <v>139.132260575</v>
+        <v>138.9739036</v>
       </c>
       <c r="Q65">
-        <v>142.522260575</v>
+        <v>142.3639036</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1986666486548904</v>
+        <v>0.202699765421754</v>
       </c>
       <c r="T65">
-        <v>2.57755130785219</v>
+        <v>2.645555450604207</v>
       </c>
       <c r="U65">
         <v>0.0503</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>14.94601393816443</v>
+        <v>14.71248247038061</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1011399155518314</v>
+        <v>0.1010452961013534</v>
       </c>
       <c r="C66">
-        <v>149.0960365338263</v>
+        <v>145.7749278142826</v>
       </c>
       <c r="D66">
-        <v>161.6680365338263</v>
+        <v>161.9449278142826</v>
       </c>
       <c r="E66">
-        <v>124.072</v>
+        <v>127.67</v>
       </c>
       <c r="F66">
-        <v>230.272</v>
+        <v>233.87</v>
       </c>
       <c r="G66">
         <v>217.7</v>
@@ -6699,28 +6699,28 @@
         <v>170.41</v>
       </c>
       <c r="M66">
-        <v>11.5826816</v>
+        <v>11.763661</v>
       </c>
       <c r="N66">
-        <v>158.8273184</v>
+        <v>158.646339</v>
       </c>
       <c r="O66">
-        <v>19.8534148</v>
+        <v>19.830792375</v>
       </c>
       <c r="P66">
-        <v>138.9739036</v>
+        <v>138.815546625</v>
       </c>
       <c r="Q66">
-        <v>142.3639036</v>
+        <v>142.205546625</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.202699765421754</v>
+        <v>0.2069633460038669</v>
       </c>
       <c r="T66">
-        <v>2.645555450604207</v>
+        <v>2.717445544370626</v>
       </c>
       <c r="U66">
         <v>0.0503</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>14.71248247038061</v>
+        <v>14.48613658622091</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1010452961013534</v>
+        <v>0.1009506766508754</v>
       </c>
       <c r="C67">
-        <v>145.7749278142826</v>
+        <v>142.4547691937183</v>
       </c>
       <c r="D67">
-        <v>161.9449278142826</v>
+        <v>162.2227691937183</v>
       </c>
       <c r="E67">
-        <v>127.67</v>
+        <v>131.268</v>
       </c>
       <c r="F67">
-        <v>233.87</v>
+        <v>237.468</v>
       </c>
       <c r="G67">
         <v>217.7</v>
@@ -6781,28 +6781,28 @@
         <v>170.41</v>
       </c>
       <c r="M67">
-        <v>11.763661</v>
+        <v>11.9446404</v>
       </c>
       <c r="N67">
-        <v>158.646339</v>
+        <v>158.4653596</v>
       </c>
       <c r="O67">
-        <v>19.830792375</v>
+        <v>19.80816995</v>
       </c>
       <c r="P67">
-        <v>138.815546625</v>
+        <v>138.65718965</v>
       </c>
       <c r="Q67">
-        <v>142.205546625</v>
+        <v>142.04718965</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2069633460038669</v>
+        <v>0.2114777254437511</v>
       </c>
       <c r="T67">
-        <v>2.717445544370626</v>
+        <v>2.793564467182128</v>
       </c>
       <c r="U67">
         <v>0.0503</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>14.48613658622091</v>
+        <v>14.26664966824786</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1009506766508754</v>
+        <v>0.1008560572003973</v>
       </c>
       <c r="C68">
-        <v>142.4547691937183</v>
+        <v>139.1355655706594</v>
       </c>
       <c r="D68">
-        <v>162.2227691937183</v>
+        <v>162.5015655706594</v>
       </c>
       <c r="E68">
-        <v>131.268</v>
+        <v>134.866</v>
       </c>
       <c r="F68">
-        <v>237.468</v>
+        <v>241.066</v>
       </c>
       <c r="G68">
         <v>217.7</v>
@@ -6863,28 +6863,28 @@
         <v>170.41</v>
       </c>
       <c r="M68">
-        <v>11.9446404</v>
+        <v>12.1256198</v>
       </c>
       <c r="N68">
-        <v>158.4653596</v>
+        <v>158.2843802</v>
       </c>
       <c r="O68">
-        <v>19.80816995</v>
+        <v>19.785547525</v>
       </c>
       <c r="P68">
-        <v>138.65718965</v>
+        <v>138.498832675</v>
       </c>
       <c r="Q68">
-        <v>142.04718965</v>
+        <v>141.888832675</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2114777254437511</v>
+        <v>0.2162657036375677</v>
       </c>
       <c r="T68">
-        <v>2.793564467182128</v>
+        <v>2.874296658042813</v>
       </c>
       <c r="U68">
         <v>0.0503</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>14.26664966824786</v>
+        <v>14.05371459857252</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1008560572003973</v>
+        <v>0.1007614377499193</v>
       </c>
       <c r="C69">
-        <v>139.1355655706594</v>
+        <v>135.8173218773644</v>
       </c>
       <c r="D69">
-        <v>162.5015655706594</v>
+        <v>162.7813218773645</v>
       </c>
       <c r="E69">
-        <v>134.866</v>
+        <v>138.464</v>
       </c>
       <c r="F69">
-        <v>241.066</v>
+        <v>244.664</v>
       </c>
       <c r="G69">
         <v>217.7</v>
@@ -6945,28 +6945,28 @@
         <v>170.41</v>
       </c>
       <c r="M69">
-        <v>12.1256198</v>
+        <v>12.3065992</v>
       </c>
       <c r="N69">
-        <v>158.2843802</v>
+        <v>158.1034008</v>
       </c>
       <c r="O69">
-        <v>19.785547525</v>
+        <v>19.7629251</v>
       </c>
       <c r="P69">
-        <v>138.498832675</v>
+        <v>138.3404757</v>
       </c>
       <c r="Q69">
-        <v>141.888832675</v>
+        <v>141.7304757</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2162657036375677</v>
+        <v>0.2213529304684979</v>
       </c>
       <c r="T69">
-        <v>2.874296658042813</v>
+        <v>2.96007461083229</v>
       </c>
       <c r="U69">
         <v>0.0503</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>14.05371459857252</v>
+        <v>13.8470423250641</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1007614377499193</v>
+        <v>0.1006668182994413</v>
       </c>
       <c r="C70">
-        <v>135.8173218773644</v>
+        <v>132.5000430801151</v>
       </c>
       <c r="D70">
-        <v>162.7813218773645</v>
+        <v>163.0620430801152</v>
       </c>
       <c r="E70">
-        <v>138.464</v>
+        <v>142.062</v>
       </c>
       <c r="F70">
-        <v>244.664</v>
+        <v>248.262</v>
       </c>
       <c r="G70">
         <v>217.7</v>
@@ -7027,28 +7027,28 @@
         <v>170.41</v>
       </c>
       <c r="M70">
-        <v>12.3065992</v>
+        <v>12.4875786</v>
       </c>
       <c r="N70">
-        <v>158.1034008</v>
+        <v>157.9224214</v>
       </c>
       <c r="O70">
-        <v>19.7629251</v>
+        <v>19.740302675</v>
       </c>
       <c r="P70">
-        <v>138.3404757</v>
+        <v>138.182118725</v>
       </c>
       <c r="Q70">
-        <v>141.7304757</v>
+        <v>141.572118725</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2213529304684979</v>
+        <v>0.2267683654820687</v>
       </c>
       <c r="T70">
-        <v>2.96007461083229</v>
+        <v>3.051386625092055</v>
       </c>
       <c r="U70">
         <v>0.0503</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>13.8470423250641</v>
+        <v>13.64636055223709</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1006668182994413</v>
+        <v>0.1005721988489632</v>
       </c>
       <c r="C71">
-        <v>132.5000430801151</v>
+        <v>129.1837341795105</v>
       </c>
       <c r="D71">
-        <v>163.0620430801152</v>
+        <v>163.3437341795106</v>
       </c>
       <c r="E71">
-        <v>142.062</v>
+        <v>145.66</v>
       </c>
       <c r="F71">
-        <v>248.262</v>
+        <v>251.86</v>
       </c>
       <c r="G71">
         <v>217.7</v>
@@ -7109,28 +7109,28 @@
         <v>170.41</v>
       </c>
       <c r="M71">
-        <v>12.4875786</v>
+        <v>12.668558</v>
       </c>
       <c r="N71">
-        <v>157.9224214</v>
+        <v>157.741442</v>
       </c>
       <c r="O71">
-        <v>19.740302675</v>
+        <v>19.71768025</v>
       </c>
       <c r="P71">
-        <v>138.182118725</v>
+        <v>138.02376175</v>
       </c>
       <c r="Q71">
-        <v>141.572118725</v>
+        <v>141.41376175</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2267683654820687</v>
+        <v>0.2325448294965442</v>
       </c>
       <c r="T71">
-        <v>3.051386625092055</v>
+        <v>3.148786106969139</v>
       </c>
       <c r="U71">
         <v>0.0503</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>13.64636055223709</v>
+        <v>13.45141254434798</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1005721988489632</v>
+        <v>0.1004775793984852</v>
       </c>
       <c r="C72">
-        <v>129.1837341795105</v>
+        <v>125.8684002107636</v>
       </c>
       <c r="D72">
-        <v>163.3437341795106</v>
+        <v>163.6264002107636</v>
       </c>
       <c r="E72">
-        <v>145.66</v>
+        <v>149.258</v>
       </c>
       <c r="F72">
-        <v>251.86</v>
+        <v>255.458</v>
       </c>
       <c r="G72">
         <v>217.7</v>
@@ -7191,28 +7191,28 @@
         <v>170.41</v>
       </c>
       <c r="M72">
-        <v>12.668558</v>
+        <v>12.8495374</v>
       </c>
       <c r="N72">
-        <v>157.741442</v>
+        <v>157.5604626</v>
       </c>
       <c r="O72">
-        <v>19.71768025</v>
+        <v>19.695057825</v>
       </c>
       <c r="P72">
-        <v>138.02376175</v>
+        <v>137.865404775</v>
       </c>
       <c r="Q72">
-        <v>141.41376175</v>
+        <v>141.255404775</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2325448294965442</v>
+        <v>0.2387196703396042</v>
       </c>
       <c r="T72">
-        <v>3.148786106969139</v>
+        <v>3.252902794492918</v>
       </c>
       <c r="U72">
         <v>0.0503</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>13.45141254434798</v>
+        <v>13.26195602963886</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1004775793984852</v>
+        <v>0.1003829599480072</v>
       </c>
       <c r="C73">
-        <v>125.8684002107636</v>
+        <v>122.5540462440017</v>
       </c>
       <c r="D73">
-        <v>163.6264002107636</v>
+        <v>163.9100462440016</v>
       </c>
       <c r="E73">
-        <v>149.258</v>
+        <v>152.856</v>
       </c>
       <c r="F73">
-        <v>255.458</v>
+        <v>259.056</v>
       </c>
       <c r="G73">
         <v>217.7</v>
@@ -7273,28 +7273,28 @@
         <v>170.41</v>
       </c>
       <c r="M73">
-        <v>12.8495374</v>
+        <v>13.0305168</v>
       </c>
       <c r="N73">
-        <v>157.5604626</v>
+        <v>157.3794832</v>
       </c>
       <c r="O73">
-        <v>19.695057825</v>
+        <v>19.6724354</v>
       </c>
       <c r="P73">
-        <v>137.865404775</v>
+        <v>137.7070478</v>
       </c>
       <c r="Q73">
-        <v>141.255404775</v>
+        <v>141.0970478</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2387196703396042</v>
+        <v>0.2453355712428828</v>
       </c>
       <c r="T73">
-        <v>3.252902794492917</v>
+        <v>3.364456388268394</v>
       </c>
       <c r="U73">
         <v>0.0503</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>13.26195602963886</v>
+        <v>13.07776219589388</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1003829599480072</v>
+        <v>0.1002883404975291</v>
       </c>
       <c r="C74">
-        <v>122.5540462440017</v>
+        <v>119.240677384569</v>
       </c>
       <c r="D74">
-        <v>163.9100462440016</v>
+        <v>164.194677384569</v>
       </c>
       <c r="E74">
-        <v>152.856</v>
+        <v>156.454</v>
       </c>
       <c r="F74">
-        <v>259.056</v>
+        <v>262.654</v>
       </c>
       <c r="G74">
         <v>217.7</v>
@@ -7355,28 +7355,28 @@
         <v>170.41</v>
       </c>
       <c r="M74">
-        <v>13.0305168</v>
+        <v>13.2114962</v>
       </c>
       <c r="N74">
-        <v>157.3794832</v>
+        <v>157.1985038</v>
       </c>
       <c r="O74">
-        <v>19.6724354</v>
+        <v>19.649812975</v>
       </c>
       <c r="P74">
-        <v>137.7070478</v>
+        <v>137.548690825</v>
       </c>
       <c r="Q74">
-        <v>141.0970478</v>
+        <v>140.938690825</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2453355712428828</v>
+        <v>0.2524415388797376</v>
       </c>
       <c r="T74">
-        <v>3.364456388268394</v>
+        <v>3.484273211212425</v>
       </c>
       <c r="U74">
         <v>0.0503</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>13.07776219589388</v>
+        <v>12.89861476855286</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1002883404975291</v>
+        <v>0.1011649710470511</v>
       </c>
       <c r="C75">
-        <v>119.240677384569</v>
+        <v>113.0428734373784</v>
       </c>
       <c r="D75">
-        <v>164.194677384569</v>
+        <v>161.5948734373784</v>
       </c>
       <c r="E75">
-        <v>156.454</v>
+        <v>160.052</v>
       </c>
       <c r="F75">
-        <v>262.654</v>
+        <v>266.252</v>
       </c>
       <c r="G75">
         <v>217.7</v>
@@ -7437,45 +7437,45 @@
         <v>170.41</v>
       </c>
       <c r="M75">
-        <v>13.2114962</v>
+        <v>13.7918536</v>
       </c>
       <c r="N75">
-        <v>157.1985038</v>
+        <v>156.6181464</v>
       </c>
       <c r="O75">
-        <v>19.649812975</v>
+        <v>19.5772683</v>
       </c>
       <c r="P75">
-        <v>137.548690825</v>
+        <v>137.0408781</v>
       </c>
       <c r="Q75">
-        <v>140.938690825</v>
+        <v>140.4308781</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2524415388797376</v>
+        <v>0.260094119411735</v>
       </c>
       <c r="T75">
-        <v>3.484273211212425</v>
+        <v>3.613306712844459</v>
       </c>
       <c r="U75">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V75">
         <v>0.125</v>
       </c>
       <c r="W75">
-        <v>0.0440125</v>
+        <v>0.045325</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y75">
-        <v>12.89861476855286</v>
+        <v>12.35584461250372</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1011649710470511</v>
+        <v>0.1010834765965731</v>
       </c>
       <c r="C76">
-        <v>113.0428734373784</v>
+        <v>109.683083590241</v>
       </c>
       <c r="D76">
-        <v>161.5948734373784</v>
+        <v>161.833083590241</v>
       </c>
       <c r="E76">
-        <v>160.052</v>
+        <v>163.65</v>
       </c>
       <c r="F76">
-        <v>266.252</v>
+        <v>269.85</v>
       </c>
       <c r="G76">
         <v>217.7</v>
@@ -7519,28 +7519,28 @@
         <v>170.41</v>
       </c>
       <c r="M76">
-        <v>13.7918536</v>
+        <v>13.97823</v>
       </c>
       <c r="N76">
-        <v>156.6181464</v>
+        <v>156.43177</v>
       </c>
       <c r="O76">
-        <v>19.5772683</v>
+        <v>19.55397125</v>
       </c>
       <c r="P76">
-        <v>137.0408781</v>
+        <v>136.87779875</v>
       </c>
       <c r="Q76">
-        <v>140.4308781</v>
+        <v>140.26779875</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.260094119411735</v>
+        <v>0.2683589063862923</v>
       </c>
       <c r="T76">
-        <v>3.613306712844459</v>
+        <v>3.752662894607055</v>
       </c>
       <c r="U76">
         <v>0.0518</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>12.35584461250372</v>
+        <v>12.19110001767034</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1010834765965731</v>
+        <v>0.101001982146095</v>
       </c>
       <c r="C77">
-        <v>109.683083590241</v>
+        <v>106.3239970803662</v>
       </c>
       <c r="D77">
-        <v>161.833083590241</v>
+        <v>162.0719970803662</v>
       </c>
       <c r="E77">
-        <v>163.65</v>
+        <v>167.248</v>
       </c>
       <c r="F77">
-        <v>269.85</v>
+        <v>273.448</v>
       </c>
       <c r="G77">
         <v>217.7</v>
@@ -7601,28 +7601,28 @@
         <v>170.41</v>
       </c>
       <c r="M77">
-        <v>13.97823</v>
+        <v>14.1646064</v>
       </c>
       <c r="N77">
-        <v>156.43177</v>
+        <v>156.2453936</v>
       </c>
       <c r="O77">
-        <v>19.55397125</v>
+        <v>19.5306742</v>
       </c>
       <c r="P77">
-        <v>136.87779875</v>
+        <v>136.7147194</v>
       </c>
       <c r="Q77">
-        <v>140.26779875</v>
+        <v>140.1047194</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2683589063862923</v>
+        <v>0.2773124256087294</v>
       </c>
       <c r="T77">
-        <v>3.752662894607055</v>
+        <v>3.903632091516535</v>
       </c>
       <c r="U77">
         <v>0.0518</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>12.19110001767034</v>
+        <v>12.03069080691152</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.101001982146095</v>
+        <v>0.100920487695617</v>
       </c>
       <c r="C78">
-        <v>106.3239970803662</v>
+        <v>102.9656170273609</v>
       </c>
       <c r="D78">
-        <v>162.0719970803662</v>
+        <v>162.3116170273609</v>
       </c>
       <c r="E78">
-        <v>167.248</v>
+        <v>170.846</v>
       </c>
       <c r="F78">
-        <v>273.448</v>
+        <v>277.046</v>
       </c>
       <c r="G78">
         <v>217.7</v>
@@ -7683,28 +7683,28 @@
         <v>170.41</v>
       </c>
       <c r="M78">
-        <v>14.1646064</v>
+        <v>14.3509828</v>
       </c>
       <c r="N78">
-        <v>156.2453936</v>
+        <v>156.0590172</v>
       </c>
       <c r="O78">
-        <v>19.5306742</v>
+        <v>19.50737715</v>
       </c>
       <c r="P78">
-        <v>136.7147194</v>
+        <v>136.55164005</v>
       </c>
       <c r="Q78">
-        <v>140.1047194</v>
+        <v>139.94164005</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2773124256087294</v>
+        <v>0.287044511720074</v>
       </c>
       <c r="T78">
-        <v>3.903632091516535</v>
+        <v>4.067729044679012</v>
       </c>
       <c r="U78">
         <v>0.0518</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>12.03069080691152</v>
+        <v>11.87444806915942</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.100920487695617</v>
+        <v>0.100838993245139</v>
       </c>
       <c r="C79">
-        <v>102.9656170273609</v>
+        <v>99.60794656930813</v>
       </c>
       <c r="D79">
-        <v>162.3116170273609</v>
+        <v>162.5519465693081</v>
       </c>
       <c r="E79">
-        <v>170.846</v>
+        <v>174.444</v>
       </c>
       <c r="F79">
-        <v>277.046</v>
+        <v>280.644</v>
       </c>
       <c r="G79">
         <v>217.7</v>
@@ -7765,28 +7765,28 @@
         <v>170.41</v>
       </c>
       <c r="M79">
-        <v>14.3509828</v>
+        <v>14.5373592</v>
       </c>
       <c r="N79">
-        <v>156.0590172</v>
+        <v>155.8726408</v>
       </c>
       <c r="O79">
-        <v>19.50737715</v>
+        <v>19.4840801</v>
       </c>
       <c r="P79">
-        <v>136.55164005</v>
+        <v>136.3885607</v>
       </c>
       <c r="Q79">
-        <v>139.94164005</v>
+        <v>139.7785607</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.287044511720074</v>
+        <v>0.29766133293245</v>
       </c>
       <c r="T79">
-        <v>4.067729044679012</v>
+        <v>4.246743902674442</v>
       </c>
       <c r="U79">
         <v>0.0518</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>11.87444806915942</v>
+        <v>11.72221155545225</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.100838993245139</v>
+        <v>0.100757498794661</v>
       </c>
       <c r="C80">
-        <v>99.60794656930813</v>
+        <v>96.25098886290476</v>
       </c>
       <c r="D80">
-        <v>162.5519465693081</v>
+        <v>162.7929888629048</v>
       </c>
       <c r="E80">
-        <v>174.444</v>
+        <v>178.042</v>
       </c>
       <c r="F80">
-        <v>280.644</v>
+        <v>284.242</v>
       </c>
       <c r="G80">
         <v>217.7</v>
@@ -7847,28 +7847,28 @@
         <v>170.41</v>
       </c>
       <c r="M80">
-        <v>14.5373592</v>
+        <v>14.7237356</v>
       </c>
       <c r="N80">
-        <v>155.8726408</v>
+        <v>155.6862644</v>
       </c>
       <c r="O80">
-        <v>19.4840801</v>
+        <v>19.46078305</v>
       </c>
       <c r="P80">
-        <v>136.3885607</v>
+        <v>136.22548135</v>
       </c>
       <c r="Q80">
-        <v>139.7785607</v>
+        <v>139.61548135</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.29766133293245</v>
+        <v>0.3092892799745761</v>
       </c>
       <c r="T80">
-        <v>4.246743902674442</v>
+        <v>4.442807794764676</v>
       </c>
       <c r="U80">
         <v>0.0518</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>11.72221155545225</v>
+        <v>11.57382913069969</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.100757498794661</v>
+        <v>0.1006760043441829</v>
       </c>
       <c r="C81">
-        <v>96.25098886290476</v>
+        <v>92.89474708359899</v>
       </c>
       <c r="D81">
-        <v>162.7929888629048</v>
+        <v>163.034747083599</v>
       </c>
       <c r="E81">
-        <v>178.042</v>
+        <v>181.64</v>
       </c>
       <c r="F81">
-        <v>284.242</v>
+        <v>287.84</v>
       </c>
       <c r="G81">
         <v>217.7</v>
@@ -7929,28 +7929,28 @@
         <v>170.41</v>
       </c>
       <c r="M81">
-        <v>14.7237356</v>
+        <v>14.910112</v>
       </c>
       <c r="N81">
-        <v>155.6862644</v>
+        <v>155.499888</v>
       </c>
       <c r="O81">
-        <v>19.46078305</v>
+        <v>19.437486</v>
       </c>
       <c r="P81">
-        <v>136.22548135</v>
+        <v>136.062402</v>
       </c>
       <c r="Q81">
-        <v>139.61548135</v>
+        <v>139.452402</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3092892799745761</v>
+        <v>0.3220800217209147</v>
       </c>
       <c r="T81">
-        <v>4.442807794764676</v>
+        <v>4.658478076063932</v>
       </c>
       <c r="U81">
         <v>0.0518</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>11.57382913069969</v>
+        <v>11.42915626656594</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1006760043441829</v>
+        <v>0.1005945098937049</v>
       </c>
       <c r="C82">
-        <v>92.89474708359899</v>
+        <v>89.53922442573008</v>
       </c>
       <c r="D82">
-        <v>163.034747083599</v>
+        <v>163.2772244257302</v>
       </c>
       <c r="E82">
-        <v>181.64</v>
+        <v>185.2380000000001</v>
       </c>
       <c r="F82">
-        <v>287.84</v>
+        <v>291.438</v>
       </c>
       <c r="G82">
         <v>217.7</v>
@@ -8011,28 +8011,28 @@
         <v>170.41</v>
       </c>
       <c r="M82">
-        <v>14.910112</v>
+        <v>15.0964884</v>
       </c>
       <c r="N82">
-        <v>155.499888</v>
+        <v>155.3135116</v>
       </c>
       <c r="O82">
-        <v>19.437486</v>
+        <v>19.41418895</v>
       </c>
       <c r="P82">
-        <v>136.062402</v>
+        <v>135.89932265</v>
       </c>
       <c r="Q82">
-        <v>139.452402</v>
+        <v>139.28932265</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3220800217209147</v>
+        <v>0.336217157335289</v>
       </c>
       <c r="T82">
-        <v>4.658478076063932</v>
+        <v>4.896850492236794</v>
       </c>
       <c r="U82">
         <v>0.0518</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>11.42915626656594</v>
+        <v>11.28805557191698</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1005945098937049</v>
+        <v>0.1005130154432269</v>
       </c>
       <c r="C83">
-        <v>89.53922442573008</v>
+        <v>86.18442410266914</v>
       </c>
       <c r="D83">
-        <v>163.2772244257302</v>
+        <v>163.5204241026692</v>
       </c>
       <c r="E83">
-        <v>185.2380000000001</v>
+        <v>188.8360000000001</v>
       </c>
       <c r="F83">
-        <v>291.438</v>
+        <v>295.0360000000001</v>
       </c>
       <c r="G83">
         <v>217.7</v>
@@ -8093,28 +8093,28 @@
         <v>170.41</v>
       </c>
       <c r="M83">
-        <v>15.0964884</v>
+        <v>15.2828648</v>
       </c>
       <c r="N83">
-        <v>155.3135116</v>
+        <v>155.1271352</v>
       </c>
       <c r="O83">
-        <v>19.41418895</v>
+        <v>19.3908919</v>
       </c>
       <c r="P83">
-        <v>135.89932265</v>
+        <v>135.7362433</v>
       </c>
       <c r="Q83">
-        <v>139.28932265</v>
+        <v>139.1262433</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.336217157335289</v>
+        <v>0.3519250857957049</v>
       </c>
       <c r="T83">
-        <v>4.896850492236794</v>
+        <v>5.161708732428862</v>
       </c>
       <c r="U83">
         <v>0.0518</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>11.28805557191698</v>
+        <v>11.15039635762531</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1005130154432269</v>
+        <v>0.1004315209927488</v>
       </c>
       <c r="C84">
-        <v>86.18442410266914</v>
+        <v>82.83034934696087</v>
       </c>
       <c r="D84">
-        <v>163.5204241026692</v>
+        <v>163.7643493469609</v>
       </c>
       <c r="E84">
-        <v>188.8360000000001</v>
+        <v>192.434</v>
       </c>
       <c r="F84">
-        <v>295.0360000000001</v>
+        <v>298.634</v>
       </c>
       <c r="G84">
         <v>217.7</v>
@@ -8175,28 +8175,28 @@
         <v>170.41</v>
       </c>
       <c r="M84">
-        <v>15.2828648</v>
+        <v>15.4692412</v>
       </c>
       <c r="N84">
-        <v>155.1271352</v>
+        <v>154.9407588</v>
       </c>
       <c r="O84">
-        <v>19.3908919</v>
+        <v>19.36759485</v>
       </c>
       <c r="P84">
-        <v>135.7362433</v>
+        <v>135.57316395</v>
       </c>
       <c r="Q84">
-        <v>139.1262433</v>
+        <v>138.96316395</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3519250857957049</v>
+        <v>0.3694810058396991</v>
       </c>
       <c r="T84">
-        <v>5.161708732428862</v>
+        <v>5.457726765584705</v>
       </c>
       <c r="U84">
         <v>0.0518</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>11.15039635762531</v>
+        <v>11.01605423283464</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1004315209927488</v>
+        <v>0.1003500265422708</v>
       </c>
       <c r="C85">
-        <v>82.83034934696087</v>
+        <v>79.47700341046681</v>
       </c>
       <c r="D85">
-        <v>163.7643493469609</v>
+        <v>164.0090034104668</v>
       </c>
       <c r="E85">
-        <v>192.434</v>
+        <v>196.032</v>
       </c>
       <c r="F85">
-        <v>298.634</v>
+        <v>302.232</v>
       </c>
       <c r="G85">
         <v>217.7</v>
@@ -8257,28 +8257,28 @@
         <v>170.41</v>
       </c>
       <c r="M85">
-        <v>15.4692412</v>
+        <v>15.6556176</v>
       </c>
       <c r="N85">
-        <v>154.9407588</v>
+        <v>154.7543824</v>
       </c>
       <c r="O85">
-        <v>19.36759485</v>
+        <v>19.3442978</v>
       </c>
       <c r="P85">
-        <v>135.57316395</v>
+        <v>135.4100846</v>
       </c>
       <c r="Q85">
-        <v>138.96316395</v>
+        <v>138.8000846</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3694810058396991</v>
+        <v>0.3892314158891927</v>
       </c>
       <c r="T85">
-        <v>5.457726765584705</v>
+        <v>5.790747052885028</v>
       </c>
       <c r="U85">
         <v>0.0518</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>11.01605423283464</v>
+        <v>10.8849107300628</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1003500265422708</v>
+        <v>0.1002685320917928</v>
       </c>
       <c r="C86">
-        <v>79.47700341046686</v>
+        <v>76.12438956451007</v>
       </c>
       <c r="D86">
-        <v>164.0090034104668</v>
+        <v>164.25438956451</v>
       </c>
       <c r="E86">
-        <v>196.032</v>
+        <v>199.63</v>
       </c>
       <c r="F86">
-        <v>302.232</v>
+        <v>305.83</v>
       </c>
       <c r="G86">
         <v>217.7</v>
@@ -8339,28 +8339,28 @@
         <v>170.41</v>
       </c>
       <c r="M86">
-        <v>15.6556176</v>
+        <v>15.841994</v>
       </c>
       <c r="N86">
-        <v>154.7543824</v>
+        <v>154.568006</v>
       </c>
       <c r="O86">
-        <v>19.3442978</v>
+        <v>19.32100075</v>
       </c>
       <c r="P86">
-        <v>135.4100846</v>
+        <v>135.24700525</v>
       </c>
       <c r="Q86">
-        <v>138.8000846</v>
+        <v>138.63700525</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3892314158891925</v>
+        <v>0.4116152139452851</v>
       </c>
       <c r="T86">
-        <v>5.790747052885024</v>
+        <v>6.168170045158723</v>
       </c>
       <c r="U86">
         <v>0.0518</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>10.8849107300628</v>
+        <v>10.75685295676794</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1002685320917928</v>
+        <v>0.1001870376413147</v>
       </c>
       <c r="C87">
-        <v>76.12438956451007</v>
+        <v>72.77251110002078</v>
       </c>
       <c r="D87">
-        <v>164.25438956451</v>
+        <v>164.5005111000208</v>
       </c>
       <c r="E87">
-        <v>199.63</v>
+        <v>203.228</v>
       </c>
       <c r="F87">
-        <v>305.83</v>
+        <v>309.428</v>
       </c>
       <c r="G87">
         <v>217.7</v>
@@ -8421,28 +8421,28 @@
         <v>170.41</v>
       </c>
       <c r="M87">
-        <v>15.841994</v>
+        <v>16.0283704</v>
       </c>
       <c r="N87">
-        <v>154.568006</v>
+        <v>154.3816296</v>
       </c>
       <c r="O87">
-        <v>19.32100075</v>
+        <v>19.2977037</v>
       </c>
       <c r="P87">
-        <v>135.24700525</v>
+        <v>135.0839259</v>
       </c>
       <c r="Q87">
-        <v>138.63700525</v>
+        <v>138.4739259</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4116152139452851</v>
+        <v>0.4371966974379624</v>
       </c>
       <c r="T87">
-        <v>6.168170045158723</v>
+        <v>6.599510607757235</v>
       </c>
       <c r="U87">
         <v>0.0518</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>10.75685295676794</v>
+        <v>10.63177327122413</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1001870376413147</v>
+        <v>0.1001055431908367</v>
       </c>
       <c r="C88">
-        <v>72.77251110002078</v>
+        <v>69.42137132768386</v>
       </c>
       <c r="D88">
-        <v>164.5005111000208</v>
+        <v>164.7473713276839</v>
       </c>
       <c r="E88">
-        <v>203.228</v>
+        <v>206.826</v>
       </c>
       <c r="F88">
-        <v>309.428</v>
+        <v>313.026</v>
       </c>
       <c r="G88">
         <v>217.7</v>
@@ -8503,28 +8503,28 @@
         <v>170.41</v>
       </c>
       <c r="M88">
-        <v>16.0283704</v>
+        <v>16.2147468</v>
       </c>
       <c r="N88">
-        <v>154.3816296</v>
+        <v>154.1952532</v>
       </c>
       <c r="O88">
-        <v>19.2977037</v>
+        <v>19.27440665</v>
       </c>
       <c r="P88">
-        <v>135.0839259</v>
+        <v>134.92084655</v>
       </c>
       <c r="Q88">
-        <v>138.4739259</v>
+        <v>138.31084655</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4371966974379624</v>
+        <v>0.4667137937756669</v>
       </c>
       <c r="T88">
-        <v>6.599510607757235</v>
+        <v>7.097211256909364</v>
       </c>
       <c r="U88">
         <v>0.0518</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>10.63177327122413</v>
+        <v>10.50956898075029</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1001055431908367</v>
+        <v>0.1000240487403587</v>
       </c>
       <c r="C89">
-        <v>69.42137132768386</v>
+        <v>66.0709735780863</v>
       </c>
       <c r="D89">
-        <v>164.7473713276839</v>
+        <v>164.9949735780864</v>
       </c>
       <c r="E89">
-        <v>206.826</v>
+        <v>210.424</v>
       </c>
       <c r="F89">
-        <v>313.026</v>
+        <v>316.624</v>
       </c>
       <c r="G89">
         <v>217.7</v>
@@ -8585,28 +8585,28 @@
         <v>170.41</v>
       </c>
       <c r="M89">
-        <v>16.2147468</v>
+        <v>16.4011232</v>
       </c>
       <c r="N89">
-        <v>154.1952532</v>
+        <v>154.0088768</v>
       </c>
       <c r="O89">
-        <v>19.27440665</v>
+        <v>19.2511096</v>
       </c>
       <c r="P89">
-        <v>134.92084655</v>
+        <v>134.7577672</v>
       </c>
       <c r="Q89">
-        <v>138.31084655</v>
+        <v>138.1477672</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4667137937756669</v>
+        <v>0.5011504061696556</v>
       </c>
       <c r="T89">
-        <v>7.097211256909364</v>
+        <v>7.677862014253516</v>
       </c>
       <c r="U89">
         <v>0.0518</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>10.50956898075029</v>
+        <v>10.39014206051449</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1000240487403587</v>
+        <v>0.09994255428988064</v>
       </c>
       <c r="C90">
-        <v>66.0709735780863</v>
+        <v>62.72132120186842</v>
       </c>
       <c r="D90">
-        <v>164.9949735780864</v>
+        <v>165.2433212018684</v>
       </c>
       <c r="E90">
-        <v>210.424</v>
+        <v>214.022</v>
       </c>
       <c r="F90">
-        <v>316.624</v>
+        <v>320.222</v>
       </c>
       <c r="G90">
         <v>217.7</v>
@@ -8667,28 +8667,28 @@
         <v>170.41</v>
       </c>
       <c r="M90">
-        <v>16.4011232</v>
+        <v>16.5874996</v>
       </c>
       <c r="N90">
-        <v>154.0088768</v>
+        <v>153.8225004</v>
       </c>
       <c r="O90">
-        <v>19.2511096</v>
+        <v>19.22781255</v>
       </c>
       <c r="P90">
-        <v>134.7577672</v>
+        <v>134.59468785</v>
       </c>
       <c r="Q90">
-        <v>138.1477672</v>
+        <v>137.98468785</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5011504061696556</v>
+        <v>0.5418482208170967</v>
       </c>
       <c r="T90">
-        <v>7.677862014253516</v>
+        <v>8.36408563656933</v>
       </c>
       <c r="U90">
         <v>0.0518</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>10.39014206051449</v>
+        <v>10.27339889129523</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.09994255428988064</v>
+        <v>0.0998610598394026</v>
       </c>
       <c r="C91">
-        <v>62.72132120186842</v>
+        <v>59.37241756987368</v>
       </c>
       <c r="D91">
-        <v>165.2433212018684</v>
+        <v>165.4924175698737</v>
       </c>
       <c r="E91">
-        <v>214.022</v>
+        <v>217.62</v>
       </c>
       <c r="F91">
-        <v>320.222</v>
+        <v>323.82</v>
       </c>
       <c r="G91">
         <v>217.7</v>
@@ -8749,28 +8749,28 @@
         <v>170.41</v>
       </c>
       <c r="M91">
-        <v>16.5874996</v>
+        <v>16.773876</v>
       </c>
       <c r="N91">
-        <v>153.8225004</v>
+        <v>153.636124</v>
       </c>
       <c r="O91">
-        <v>19.22781255</v>
+        <v>19.2045155</v>
       </c>
       <c r="P91">
-        <v>134.59468785</v>
+        <v>134.4316085</v>
       </c>
       <c r="Q91">
-        <v>137.98468785</v>
+        <v>137.8216085</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5418482208170967</v>
+        <v>0.5906855983940261</v>
       </c>
       <c r="T91">
-        <v>8.36408563656933</v>
+        <v>9.187553983348309</v>
       </c>
       <c r="U91">
         <v>0.0518</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>10.27339889129523</v>
+        <v>10.15925001472528</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.0998610598394026</v>
+        <v>0.09977956538892457</v>
       </c>
       <c r="C92">
-        <v>59.37241756987368</v>
+        <v>56.0242660733021</v>
       </c>
       <c r="D92">
-        <v>165.4924175698737</v>
+        <v>165.7422660733021</v>
       </c>
       <c r="E92">
-        <v>217.62</v>
+        <v>221.218</v>
       </c>
       <c r="F92">
-        <v>323.82</v>
+        <v>327.418</v>
       </c>
       <c r="G92">
         <v>217.7</v>
@@ -8831,28 +8831,28 @@
         <v>170.41</v>
       </c>
       <c r="M92">
-        <v>16.773876</v>
+        <v>16.9602524</v>
       </c>
       <c r="N92">
-        <v>153.636124</v>
+        <v>153.4497476</v>
       </c>
       <c r="O92">
-        <v>19.2045155</v>
+        <v>19.18121845</v>
       </c>
       <c r="P92">
-        <v>134.4316085</v>
+        <v>134.26852915</v>
       </c>
       <c r="Q92">
-        <v>137.8216085</v>
+        <v>137.65852915</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5906855983940261</v>
+        <v>0.6503757265436065</v>
       </c>
       <c r="T92">
-        <v>9.187553983348309</v>
+        <v>10.19401529607817</v>
       </c>
       <c r="U92">
         <v>0.0518</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>10.15925001472528</v>
+        <v>10.04760990467335</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.09977956538892457</v>
+        <v>0.09969807093844654</v>
       </c>
       <c r="C93">
-        <v>56.0242660733021</v>
+        <v>52.67687012386358</v>
       </c>
       <c r="D93">
-        <v>165.7422660733021</v>
+        <v>165.9928701238636</v>
       </c>
       <c r="E93">
-        <v>221.218</v>
+        <v>224.816</v>
       </c>
       <c r="F93">
-        <v>327.418</v>
+        <v>331.016</v>
       </c>
       <c r="G93">
         <v>217.7</v>
@@ -8913,28 +8913,28 @@
         <v>170.41</v>
       </c>
       <c r="M93">
-        <v>16.9602524</v>
+        <v>17.1466288</v>
       </c>
       <c r="N93">
-        <v>153.4497476</v>
+        <v>153.2633712</v>
       </c>
       <c r="O93">
-        <v>19.18121845</v>
+        <v>19.1579214</v>
       </c>
       <c r="P93">
-        <v>134.26852915</v>
+        <v>134.1054498</v>
       </c>
       <c r="Q93">
-        <v>137.65852915</v>
+        <v>137.4954498</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6503757265436065</v>
+        <v>0.7249883867305822</v>
       </c>
       <c r="T93">
-        <v>10.19401529607817</v>
+        <v>11.4520919369905</v>
       </c>
       <c r="U93">
         <v>0.0518</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>10.04760990467335</v>
+        <v>9.938396753535599</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.09969807093844654</v>
+        <v>0.09961657648796851</v>
       </c>
       <c r="C94">
-        <v>52.67687012386358</v>
+        <v>49.3302331539337</v>
       </c>
       <c r="D94">
-        <v>165.9928701238636</v>
+        <v>166.2442331539337</v>
       </c>
       <c r="E94">
-        <v>224.816</v>
+        <v>228.414</v>
       </c>
       <c r="F94">
-        <v>331.016</v>
+        <v>334.614</v>
       </c>
       <c r="G94">
         <v>217.7</v>
@@ -8995,28 +8995,28 @@
         <v>170.41</v>
       </c>
       <c r="M94">
-        <v>17.1466288</v>
+        <v>17.3330052</v>
       </c>
       <c r="N94">
-        <v>153.2633712</v>
+        <v>153.0769948</v>
       </c>
       <c r="O94">
-        <v>19.1579214</v>
+        <v>19.13462435</v>
       </c>
       <c r="P94">
-        <v>134.1054498</v>
+        <v>133.94237045</v>
       </c>
       <c r="Q94">
-        <v>137.4954498</v>
+        <v>137.33237045</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.7249883867305822</v>
+        <v>0.8209189498281222</v>
       </c>
       <c r="T94">
-        <v>11.4520919369905</v>
+        <v>13.06961904673493</v>
       </c>
       <c r="U94">
         <v>0.0518</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>9.938396753535599</v>
+        <v>9.831532272314787</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.09961657648796851</v>
+        <v>0.1009333320374905</v>
       </c>
       <c r="C95">
-        <v>49.3302331539337</v>
+        <v>41.76180349746721</v>
       </c>
       <c r="D95">
-        <v>166.2442331539337</v>
+        <v>162.2738034974673</v>
       </c>
       <c r="E95">
-        <v>228.414</v>
+        <v>232.0120000000001</v>
       </c>
       <c r="F95">
-        <v>334.614</v>
+        <v>338.212</v>
       </c>
       <c r="G95">
         <v>217.7</v>
@@ -9077,45 +9077,45 @@
         <v>170.41</v>
       </c>
       <c r="M95">
-        <v>17.3330052</v>
+        <v>18.094342</v>
       </c>
       <c r="N95">
-        <v>153.0769948</v>
+        <v>152.315658</v>
       </c>
       <c r="O95">
-        <v>19.13462435</v>
+        <v>19.03945725</v>
       </c>
       <c r="P95">
-        <v>133.94237045</v>
+        <v>133.27620075</v>
       </c>
       <c r="Q95">
-        <v>137.33237045</v>
+        <v>136.66620075</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.8209189498281222</v>
+        <v>0.9488263672915087</v>
       </c>
       <c r="T95">
-        <v>13.06961904673493</v>
+        <v>15.22632185972749</v>
       </c>
       <c r="U95">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V95">
         <v>0.125</v>
       </c>
       <c r="W95">
-        <v>0.045325</v>
+        <v>0.0468125</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y95">
-        <v>9.831532272314787</v>
+        <v>9.417861119238268</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1009333320374905</v>
+        <v>0.1008667125870124</v>
       </c>
       <c r="C96">
-        <v>41.76180349746721</v>
+        <v>38.36012158344153</v>
       </c>
       <c r="D96">
-        <v>162.2738034974673</v>
+        <v>162.4701215834416</v>
       </c>
       <c r="E96">
-        <v>232.0120000000001</v>
+        <v>235.6100000000001</v>
       </c>
       <c r="F96">
-        <v>338.212</v>
+        <v>341.8100000000001</v>
       </c>
       <c r="G96">
         <v>217.7</v>
@@ -9159,28 +9159,28 @@
         <v>170.41</v>
       </c>
       <c r="M96">
-        <v>18.094342</v>
+        <v>18.286835</v>
       </c>
       <c r="N96">
-        <v>152.315658</v>
+        <v>152.123165</v>
       </c>
       <c r="O96">
-        <v>19.03945725</v>
+        <v>19.015395625</v>
       </c>
       <c r="P96">
-        <v>133.27620075</v>
+        <v>133.107769375</v>
       </c>
       <c r="Q96">
-        <v>136.66620075</v>
+        <v>136.497769375</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.9488263672915087</v>
+        <v>1.127896751740251</v>
       </c>
       <c r="T96">
-        <v>15.22632185972749</v>
+        <v>18.24570579791709</v>
       </c>
       <c r="U96">
         <v>0.0535</v>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>9.417861119238268</v>
+        <v>9.318725739035759</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1008667125870124</v>
+        <v>0.1008000931365344</v>
       </c>
       <c r="C97">
-        <v>38.36012158344153</v>
+        <v>34.95891525417449</v>
       </c>
       <c r="D97">
-        <v>162.4701215834416</v>
+        <v>162.6669152541745</v>
       </c>
       <c r="E97">
-        <v>235.6100000000001</v>
+        <v>239.208</v>
       </c>
       <c r="F97">
-        <v>341.8100000000001</v>
+        <v>345.408</v>
       </c>
       <c r="G97">
         <v>217.7</v>
@@ -9241,28 +9241,28 @@
         <v>170.41</v>
       </c>
       <c r="M97">
-        <v>18.286835</v>
+        <v>18.479328</v>
       </c>
       <c r="N97">
-        <v>152.123165</v>
+        <v>151.930672</v>
       </c>
       <c r="O97">
-        <v>19.015395625</v>
+        <v>18.991334</v>
       </c>
       <c r="P97">
-        <v>133.107769375</v>
+        <v>132.939338</v>
       </c>
       <c r="Q97">
-        <v>136.497769375</v>
+        <v>136.329338</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.127896751740251</v>
+        <v>1.396502328413363</v>
       </c>
       <c r="T97">
-        <v>18.24570579791709</v>
+        <v>22.77478170520148</v>
       </c>
       <c r="U97">
         <v>0.0535</v>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>9.318725739035759</v>
+        <v>9.221655679254139</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1008000931365344</v>
+        <v>0.1007334736860564</v>
       </c>
       <c r="C98">
-        <v>34.95891525417437</v>
+        <v>31.55818623993292</v>
       </c>
       <c r="D98">
-        <v>162.6669152541744</v>
+        <v>162.864186239933</v>
       </c>
       <c r="E98">
-        <v>239.208</v>
+        <v>242.806</v>
       </c>
       <c r="F98">
-        <v>345.408</v>
+        <v>349.006</v>
       </c>
       <c r="G98">
         <v>217.7</v>
@@ -9323,28 +9323,28 @@
         <v>170.41</v>
       </c>
       <c r="M98">
-        <v>18.479328</v>
+        <v>18.671821</v>
       </c>
       <c r="N98">
-        <v>151.930672</v>
+        <v>151.738179</v>
       </c>
       <c r="O98">
-        <v>18.991334</v>
+        <v>18.967272375</v>
       </c>
       <c r="P98">
-        <v>132.939338</v>
+        <v>132.770906625</v>
       </c>
       <c r="Q98">
-        <v>136.329338</v>
+        <v>136.160906625</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.396502328413359</v>
+        <v>1.844178289535211</v>
       </c>
       <c r="T98">
-        <v>22.77478170520142</v>
+        <v>30.32324155067538</v>
       </c>
       <c r="U98">
         <v>0.0535</v>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>9.221655679254139</v>
+        <v>9.126587064004095</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1007334736860564</v>
+        <v>0.1006668542355783</v>
       </c>
       <c r="C99">
-        <v>31.55818623993292</v>
+        <v>28.15793627938803</v>
       </c>
       <c r="D99">
-        <v>162.864186239933</v>
+        <v>163.061936279388</v>
       </c>
       <c r="E99">
-        <v>242.806</v>
+        <v>246.404</v>
       </c>
       <c r="F99">
-        <v>349.006</v>
+        <v>352.604</v>
       </c>
       <c r="G99">
         <v>217.7</v>
@@ -9405,28 +9405,28 @@
         <v>170.41</v>
       </c>
       <c r="M99">
-        <v>18.671821</v>
+        <v>18.864314</v>
       </c>
       <c r="N99">
-        <v>151.738179</v>
+        <v>151.545686</v>
       </c>
       <c r="O99">
-        <v>18.967272375</v>
+        <v>18.94321075</v>
       </c>
       <c r="P99">
-        <v>132.770906625</v>
+        <v>132.60247525</v>
       </c>
       <c r="Q99">
-        <v>136.160906625</v>
+        <v>135.99247525</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.844178289535211</v>
+        <v>2.739530211778915</v>
       </c>
       <c r="T99">
-        <v>30.32324155067538</v>
+        <v>45.42016124162328</v>
       </c>
       <c r="U99">
         <v>0.0535</v>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>9.126587064004095</v>
+        <v>9.033458624575482</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1006668542355783</v>
+        <v>0.1006002347851003</v>
       </c>
       <c r="C100">
-        <v>28.15793627938803</v>
+        <v>24.75816711966473</v>
       </c>
       <c r="D100">
-        <v>163.061936279388</v>
+        <v>163.2601671196647</v>
       </c>
       <c r="E100">
-        <v>246.404</v>
+        <v>250.002</v>
       </c>
       <c r="F100">
-        <v>352.604</v>
+        <v>356.202</v>
       </c>
       <c r="G100">
         <v>217.7</v>
@@ -9487,28 +9487,28 @@
         <v>170.41</v>
       </c>
       <c r="M100">
-        <v>18.864314</v>
+        <v>19.056807</v>
       </c>
       <c r="N100">
-        <v>151.545686</v>
+        <v>151.353193</v>
       </c>
       <c r="O100">
-        <v>18.94321075</v>
+        <v>18.919149125</v>
       </c>
       <c r="P100">
-        <v>132.60247525</v>
+        <v>132.434043875</v>
       </c>
       <c r="Q100">
-        <v>135.99247525</v>
+        <v>135.824043875</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.739530211778915</v>
+        <v>5.425585978510028</v>
       </c>
       <c r="T100">
-        <v>45.42016124162328</v>
+        <v>90.71092031446702</v>
       </c>
       <c r="U100">
         <v>0.0535</v>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>9.033458624575482</v>
+        <v>8.942211567761589</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1006002347851003</v>
-      </c>
-      <c r="C101">
-        <v>24.75816711966473</v>
-      </c>
-      <c r="D101">
-        <v>163.2601671196647</v>
-      </c>
-      <c r="E101">
-        <v>250.002</v>
-      </c>
-      <c r="F101">
-        <v>356.202</v>
-      </c>
-      <c r="G101">
-        <v>217.7</v>
-      </c>
-      <c r="H101">
-        <v>253.6</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>173.8</v>
-      </c>
-      <c r="K101">
-        <v>3.39</v>
-      </c>
-      <c r="L101">
-        <v>170.41</v>
-      </c>
-      <c r="M101">
-        <v>19.056807</v>
-      </c>
-      <c r="N101">
-        <v>151.353193</v>
-      </c>
-      <c r="O101">
-        <v>18.919149125</v>
-      </c>
-      <c r="P101">
-        <v>132.434043875</v>
-      </c>
-      <c r="Q101">
-        <v>135.824043875</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.425585978510028</v>
-      </c>
-      <c r="T101">
-        <v>90.71092031446702</v>
-      </c>
-      <c r="U101">
-        <v>0.0535</v>
-      </c>
-      <c r="V101">
-        <v>0.125</v>
-      </c>
-      <c r="W101">
-        <v>0.0468125</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>A1/A+</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>8.942211567761589</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
